--- a/Max 3.xlsx
+++ b/Max 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90232C7-3522-4DFB-A058-811BA2AB990B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2883E520-4449-4E7B-9C3D-AD8A7B25107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15990" yWindow="1290" windowWidth="9585" windowHeight="12810" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUR " sheetId="11" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>31/3/2026</t>
+  </si>
+  <si>
+    <t> 2026-04-14</t>
   </si>
 </sst>
 </file>
@@ -216,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -272,6 +275,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14425,7 +14432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0DCE6A-E542-4A83-ACFA-B4956F29450C}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="16" customWidth="1"/>
@@ -14471,7 +14478,7 @@
         <v>162331</v>
       </c>
       <c r="D2" s="11">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
         <v>73589</v>
       </c>
       <c r="E2" s="1">
@@ -14481,7 +14488,7 @@
         <v>1584</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G27" si="1">E2-F2</f>
         <v>-18206</v>
       </c>
     </row>
@@ -14983,6 +14990,131 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>-8772</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>200946</v>
+      </c>
+      <c r="C23" s="7">
+        <v>208487</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>-7541</v>
+      </c>
+      <c r="E23">
+        <v>778</v>
+      </c>
+      <c r="F23" s="7">
+        <v>8826</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-8048</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>129517</v>
+      </c>
+      <c r="C24" s="7">
+        <v>64442</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>65075</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-8442</v>
+      </c>
+      <c r="F24" s="7">
+        <v>-2704</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-5738</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B25" s="7">
+        <v>214639</v>
+      </c>
+      <c r="C25" s="7">
+        <v>188621</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>26018</v>
+      </c>
+      <c r="E25" s="7">
+        <v>13693</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-19866</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>33559</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B26" s="7">
+        <v>217407</v>
+      </c>
+      <c r="C26" s="7">
+        <v>176083</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>41324</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2768</v>
+      </c>
+      <c r="F26" s="7">
+        <v>-12538</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="1"/>
+        <v>15306</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B27" s="7">
+        <v>217091</v>
+      </c>
+      <c r="C27" s="7">
+        <v>181379</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>35712</v>
+      </c>
+      <c r="E27">
+        <v>-316</v>
+      </c>
+      <c r="F27" s="7">
+        <v>5296</v>
+      </c>
+      <c r="G27" s="22">
+        <f t="shared" si="1"/>
+        <v>-5612</v>
       </c>
     </row>
   </sheetData>
@@ -14994,7 +15126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E049AD9-8C60-4A1C-9327-32192CC888AD}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="16" customWidth="1"/>
@@ -15040,7 +15172,7 @@
         <v>31631</v>
       </c>
       <c r="D2" s="11">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D26" si="0">B2-C2</f>
         <v>-15627</v>
       </c>
       <c r="E2" s="1">
@@ -15050,7 +15182,7 @@
         <v>-576</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G26" si="1">E2-F2</f>
         <v>-65</v>
       </c>
     </row>
@@ -15552,6 +15684,106 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>23084</v>
+      </c>
+      <c r="C23" s="7">
+        <v>17573</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>5511</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1376</v>
+      </c>
+      <c r="F23">
+        <v>-454</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>18970</v>
+      </c>
+      <c r="C24" s="7">
+        <v>13800</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>5170</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4114</v>
+      </c>
+      <c r="F24" s="7">
+        <v>-3773</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>17617</v>
+      </c>
+      <c r="C25" s="7">
+        <v>12634</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>4983</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1353</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-1166</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>-187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>17180</v>
+      </c>
+      <c r="C26" s="7">
+        <v>12672</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>4508</v>
+      </c>
+      <c r="E26">
+        <v>-437</v>
+      </c>
+      <c r="F26">
+        <v>38</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="1"/>
+        <v>-475</v>
       </c>
     </row>
   </sheetData>
@@ -15563,7 +15795,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A64D1E-BA3D-43E2-BF69-69E226E6EEE7}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="26" customWidth="1"/>
@@ -15634,7 +15866,7 @@
         <v>121577</v>
       </c>
       <c r="D3" s="11">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D25" si="0">B3-C3</f>
         <v>-75856</v>
       </c>
       <c r="E3" s="3">
@@ -15644,7 +15876,7 @@
         <v>-164</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G25" si="1">E3-F3</f>
         <v>2771</v>
       </c>
     </row>
@@ -16121,6 +16353,81 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>7658</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>137959</v>
+      </c>
+      <c r="C23" s="7">
+        <v>67146</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>70813</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3816</v>
+      </c>
+      <c r="F23" s="7">
+        <v>6877</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-10693</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B24" s="7">
+        <v>128811</v>
+      </c>
+      <c r="C24" s="7">
+        <v>63994</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>64817</v>
+      </c>
+      <c r="E24">
+        <v>-706</v>
+      </c>
+      <c r="F24">
+        <v>-448</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B25" s="7">
+        <v>136909</v>
+      </c>
+      <c r="C25" s="7">
+        <v>65040</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>71869</v>
+      </c>
+      <c r="E25" s="7">
+        <v>8098</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1046</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>7052</v>
       </c>
     </row>
   </sheetData>
@@ -16131,7 +16438,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484D440D-6E6B-4B12-86E6-BEF7B583A71E}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" style="16" customWidth="1"/>
@@ -16202,7 +16509,7 @@
         <v>40931</v>
       </c>
       <c r="D3" s="11">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D26" si="0">B3-C3</f>
         <v>-32185</v>
       </c>
       <c r="E3" s="3">
@@ -16212,7 +16519,7 @@
         <v>-2521</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
         <v>3864</v>
       </c>
     </row>
@@ -16689,6 +16996,106 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>-2774</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>10586</v>
+      </c>
+      <c r="C23" s="7">
+        <v>41280</v>
+      </c>
+      <c r="D23" s="28">
+        <f t="shared" si="0"/>
+        <v>-30694</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1271</v>
+      </c>
+      <c r="F23" s="7">
+        <v>2094</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-823</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>9637</v>
+      </c>
+      <c r="C24" s="7">
+        <v>43734</v>
+      </c>
+      <c r="D24" s="28">
+        <f t="shared" si="0"/>
+        <v>-34097</v>
+      </c>
+      <c r="E24">
+        <v>-949</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2454</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-3403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>8372</v>
+      </c>
+      <c r="C25" s="7">
+        <v>41645</v>
+      </c>
+      <c r="D25" s="28">
+        <f t="shared" si="0"/>
+        <v>-33273</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1265</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-2089</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>824</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>6359</v>
+      </c>
+      <c r="C26" s="7">
+        <v>41580</v>
+      </c>
+      <c r="D26" s="28">
+        <f t="shared" si="0"/>
+        <v>-35221</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2013</v>
+      </c>
+      <c r="F26">
+        <v>-65</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="1"/>
+        <v>-1948</v>
       </c>
     </row>
   </sheetData>
@@ -16698,7 +17105,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E55D1F-7511-410A-9BDB-6D70A2FC177B}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="16" customWidth="1"/>
@@ -16744,7 +17151,7 @@
         <v>133427</v>
       </c>
       <c r="D2" s="15">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D26" si="0">B2-C2</f>
         <v>-81004</v>
       </c>
       <c r="E2" s="1">
@@ -17204,7 +17611,7 @@
         <v>-23659</v>
       </c>
       <c r="G20" s="1">
-        <f>E20-F20</f>
+        <f t="shared" ref="G20:G26" si="2">E20-F20</f>
         <v>18682</v>
       </c>
     </row>
@@ -17229,7 +17636,7 @@
         <v>-4927</v>
       </c>
       <c r="G21" s="1">
-        <f>E21-F21</f>
+        <f t="shared" si="2"/>
         <v>7093</v>
       </c>
     </row>
@@ -17254,8 +17661,108 @@
         <v>912</v>
       </c>
       <c r="G22" s="22">
-        <f>E22-F22</f>
+        <f t="shared" si="2"/>
         <v>3933</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>47344</v>
+      </c>
+      <c r="C23" s="7">
+        <v>103698</v>
+      </c>
+      <c r="D23" s="16">
+        <f t="shared" si="0"/>
+        <v>-56354</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3960</v>
+      </c>
+      <c r="F23">
+        <v>-271</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="2"/>
+        <v>-3689</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>54947</v>
+      </c>
+      <c r="C24" s="7">
+        <v>109671</v>
+      </c>
+      <c r="D24" s="16">
+        <f t="shared" si="0"/>
+        <v>-54724</v>
+      </c>
+      <c r="E24" s="7">
+        <v>7603</v>
+      </c>
+      <c r="F24" s="7">
+        <v>5973</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="2"/>
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>63086</v>
+      </c>
+      <c r="C25" s="7">
+        <v>115125</v>
+      </c>
+      <c r="D25" s="16">
+        <f t="shared" si="0"/>
+        <v>-52039</v>
+      </c>
+      <c r="E25" s="7">
+        <v>8139</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5454</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="2"/>
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>59577</v>
+      </c>
+      <c r="C26" s="7">
+        <v>120216</v>
+      </c>
+      <c r="D26" s="16">
+        <f t="shared" si="0"/>
+        <v>-60639</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3509</v>
+      </c>
+      <c r="F26" s="7">
+        <v>5091</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="2"/>
+        <v>-8600</v>
       </c>
     </row>
   </sheetData>
@@ -17267,7 +17774,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8ECBF1-DFF0-4C27-BC6C-1C623368F16D}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="16" bestFit="1" customWidth="1"/>
@@ -17323,7 +17830,7 @@
         <v>4958</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G26" si="1">E2-F2</f>
         <v>-2789</v>
       </c>
     </row>
@@ -17828,17 +18335,105 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="29">
+        <v>91560</v>
+      </c>
+      <c r="C23" s="29">
+        <v>185302</v>
+      </c>
+      <c r="D23" s="16">
+        <f>B23-C23</f>
+        <v>-93742</v>
+      </c>
+      <c r="E23" s="29">
+        <v>-3796</v>
+      </c>
+      <c r="F23" s="29">
+        <v>17074</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="1"/>
+        <v>-20870</v>
+      </c>
       <c r="H23" s="2"/>
     </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7">
+        <v>102114</v>
+      </c>
+      <c r="C24" s="7">
+        <v>185322</v>
+      </c>
+      <c r="D24" s="16">
+        <f>B24-C24</f>
+        <v>-83208</v>
+      </c>
+      <c r="E24" s="7">
+        <v>10554</v>
+      </c>
+      <c r="F24">
+        <v>20</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>10534</v>
+      </c>
+    </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>101386</v>
+      </c>
+      <c r="C25" s="7">
+        <v>195846</v>
+      </c>
+      <c r="D25" s="16">
+        <f>B25-C25</f>
+        <v>-94460</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-728</v>
+      </c>
+      <c r="F25" s="29">
+        <v>10524</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="1"/>
+        <v>-11252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>106530</v>
+      </c>
+      <c r="C26" s="7">
+        <v>208589</v>
+      </c>
+      <c r="D26" s="16">
+        <f>B26-C26</f>
+        <v>-102059</v>
+      </c>
+      <c r="E26" s="7">
+        <v>5144</v>
+      </c>
+      <c r="F26" s="7">
+        <v>12743</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="1"/>
+        <v>-7599</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -17849,7 +18444,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDC40EE-8D54-47CC-9557-EC14C0D36988}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="16" customWidth="1"/>
@@ -17920,7 +18515,7 @@
         <v>173351</v>
       </c>
       <c r="D3" s="12">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D26" si="0">B3-C3</f>
         <v>-149099</v>
       </c>
       <c r="E3" s="3">
@@ -17930,7 +18525,7 @@
         <v>-7435</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
         <v>8536</v>
       </c>
     </row>
@@ -18410,10 +19005,104 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="7"/>
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>60714</v>
+      </c>
+      <c r="C23" s="7">
+        <v>116362</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>-55648</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4293</v>
+      </c>
+      <c r="F23" s="7">
+        <v>27257</v>
+      </c>
+      <c r="G23" s="27">
+        <f t="shared" si="1"/>
+        <v>-22964</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="7"/>
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>54249</v>
+      </c>
+      <c r="C24" s="7">
+        <v>132521</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>-78272</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-6465</v>
+      </c>
+      <c r="F24" s="7">
+        <v>16159</v>
+      </c>
+      <c r="G24" s="27">
+        <f t="shared" si="1"/>
+        <v>-22624</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>60889</v>
+      </c>
+      <c r="C25" s="7">
+        <v>119723</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>-58834</v>
+      </c>
+      <c r="E25" s="7">
+        <v>6640</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-12798</v>
+      </c>
+      <c r="G25" s="27">
+        <f t="shared" si="1"/>
+        <v>19438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>66517</v>
+      </c>
+      <c r="C26" s="7">
+        <v>104993</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>-38476</v>
+      </c>
+      <c r="E26" s="7">
+        <v>5628</v>
+      </c>
+      <c r="F26" s="7">
+        <v>-14730</v>
+      </c>
+      <c r="G26" s="27">
+        <f t="shared" si="1"/>
+        <v>20358</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18423,7 +19112,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A07693-2708-497B-89D5-86A56CB2CAAA}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -18494,7 +19183,7 @@
         <v>73468</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D26" si="0">B3-C3</f>
         <v>-49257</v>
       </c>
       <c r="E3" s="7">
@@ -18504,7 +19193,7 @@
         <v>722</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
         <v>-5188</v>
       </c>
     </row>
@@ -18981,6 +19670,106 @@
       <c r="G22">
         <f t="shared" si="1"/>
         <v>-1582</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>12636</v>
+      </c>
+      <c r="C23" s="7">
+        <v>48711</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>-36075</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1973</v>
+      </c>
+      <c r="F23" s="7">
+        <v>9460</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>-7487</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="20">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>10112</v>
+      </c>
+      <c r="C24" s="7">
+        <v>52388</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="0"/>
+        <v>-42276</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2524</v>
+      </c>
+      <c r="F24" s="7">
+        <v>3677</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>-6201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>7917</v>
+      </c>
+      <c r="C25" s="7">
+        <v>56371</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" si="0"/>
+        <v>-48454</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2195</v>
+      </c>
+      <c r="F25" s="7">
+        <v>3983</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>-6178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="20">
+        <v>46140</v>
+      </c>
+      <c r="B26" s="7">
+        <v>9044</v>
+      </c>
+      <c r="C26" s="7">
+        <v>55366</v>
+      </c>
+      <c r="D26" s="7">
+        <f t="shared" si="0"/>
+        <v>-46322</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1127</v>
+      </c>
+      <c r="F26" s="7">
+        <v>-1005</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>2132</v>
       </c>
     </row>
   </sheetData>

--- a/Max 3.xlsx
+++ b/Max 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2883E520-4449-4E7B-9C3D-AD8A7B25107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E5C2D6-CB4B-4949-88C1-2E7DBDF75C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15990" yWindow="1290" windowWidth="9585" windowHeight="12810" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUR " sheetId="11" r:id="rId1"/>
@@ -21,13 +21,15 @@
     <sheet name="JPY" sheetId="8" r:id="rId6"/>
     <sheet name="CAD" sheetId="16" r:id="rId7"/>
     <sheet name="NZD" sheetId="18" r:id="rId8"/>
+    <sheet name="XAU" sheetId="19" r:id="rId9"/>
+    <sheet name="BTC" sheetId="20" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -15124,6 +15126,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB577F0-051C-45DD-9491-CB7C4AFFE320}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
+        <v>46140</v>
+      </c>
+      <c r="B2" s="7">
+        <v>17431</v>
+      </c>
+      <c r="C2" s="7">
+        <v>15039</v>
+      </c>
+      <c r="D2" s="7">
+        <f>B2-C2</f>
+        <v>2392</v>
+      </c>
+      <c r="E2">
+        <v>334</v>
+      </c>
+      <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <f>E2-F2</f>
+        <v>321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E049AD9-8C60-4A1C-9327-32192CC888AD}">
   <dimension ref="A1:G26"/>
@@ -18295,7 +18364,7 @@
         <v>161077</v>
       </c>
       <c r="D21" s="15">
-        <f>B21-C21</f>
+        <f t="shared" ref="D21:D26" si="2">B21-C21</f>
         <v>-62806</v>
       </c>
       <c r="E21" s="3">
@@ -18320,7 +18389,7 @@
         <v>168228</v>
       </c>
       <c r="D22" s="16">
-        <f>B22-C22</f>
+        <f t="shared" si="2"/>
         <v>-72872</v>
       </c>
       <c r="E22" s="2">
@@ -18345,7 +18414,7 @@
         <v>185302</v>
       </c>
       <c r="D23" s="16">
-        <f>B23-C23</f>
+        <f t="shared" si="2"/>
         <v>-93742</v>
       </c>
       <c r="E23" s="29">
@@ -18371,7 +18440,7 @@
         <v>185322</v>
       </c>
       <c r="D24" s="16">
-        <f>B24-C24</f>
+        <f t="shared" si="2"/>
         <v>-83208</v>
       </c>
       <c r="E24" s="7">
@@ -18396,7 +18465,7 @@
         <v>195846</v>
       </c>
       <c r="D25" s="16">
-        <f>B25-C25</f>
+        <f t="shared" si="2"/>
         <v>-94460</v>
       </c>
       <c r="E25" s="2">
@@ -18421,7 +18490,7 @@
         <v>208589</v>
       </c>
       <c r="D26" s="16">
-        <f>B26-C26</f>
+        <f t="shared" si="2"/>
         <v>-102059</v>
       </c>
       <c r="E26" s="7">
@@ -19775,4 +19844,71 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC5BCC2-0E7D-47AA-8D33-415F235882BE}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
+        <v>46140</v>
+      </c>
+      <c r="B2" s="7">
+        <v>211818</v>
+      </c>
+      <c r="C2" s="7">
+        <v>52247</v>
+      </c>
+      <c r="D2" s="7">
+        <f>B2-C2</f>
+        <v>159571</v>
+      </c>
+      <c r="E2" s="7">
+        <v>-1075</v>
+      </c>
+      <c r="F2" s="7">
+        <v>3360</v>
+      </c>
+      <c r="G2" s="7">
+        <f>E2-F2</f>
+        <v>-4435</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Max 3.xlsx
+++ b/Max 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E5C2D6-CB4B-4949-88C1-2E7DBDF75C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A0827E-0005-4C7E-BB10-4CB054EF8D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Max 3.xlsx
+++ b/Max 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADDA407-D799-480E-9D79-1F719D56EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EBFEE6-1A73-42A5-8608-FC56469CDF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUR " sheetId="11" r:id="rId1"/>
@@ -24,20 +24,12 @@
     <sheet name="XAU" sheetId="19" r:id="rId9"/>
     <sheet name="BTC" sheetId="20" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">NZD!$A$2:$A$26</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">NZD!$D$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">NZD!$D$2:$D$26</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">NZD!$A$2:$A$26</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">NZD!$D$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">NZD!$D$2:$D$26</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -104,12 +96,15 @@
   <si>
     <t> 2026-04-14</t>
   </si>
+  <si>
+    <t>a</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +164,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -184,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -207,53 +230,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -274,21 +255,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -301,13 +269,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -333,17 +294,31 @@
     <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,16 +364,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -427,15 +402,50 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -481,13 +491,14 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525">
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
                         <a:schemeClr val="tx1">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -497,7 +508,7 @@
           </c:dLbls>
           <c:trendline>
             <c:spPr>
-              <a:ln w="15875" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -510,9 +521,9 @@
           </c:trendline>
           <c:cat>
             <c:strRef>
-              <c:f>'EUR '!$A$2:$A$27</c:f>
+              <c:f>'EUR '!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>10/11/2025</c:v>
                 </c:pt>
@@ -590,16 +601,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>4/28/2026</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5/5/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'EUR '!$D$2:$D$27</c:f>
+              <c:f>'EUR '!$D$2:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>73589</c:v>
                 </c:pt>
@@ -677,6 +691,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>35712</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>32202</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -696,8 +713,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="80"/>
-        <c:overlap val="25"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
         <c:axId val="1182759728"/>
         <c:axId val="1182765488"/>
       </c:barChart>
@@ -709,16 +726,16 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -730,7 +747,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -764,8 +781,8 @@
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -774,7 +791,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -789,7 +806,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -829,7 +846,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -2206,6 +2223,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-BE30-411D-95E6-4823C8A44593}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -2260,6 +2282,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-BE30-411D-95E6-4823C8A44593}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
@@ -2314,6 +2341,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-BE30-411D-95E6-4823C8A44593}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
@@ -2368,6 +2400,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-BE30-411D-95E6-4823C8A44593}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
@@ -2425,6 +2462,73 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-BE30-411D-95E6-4823C8A44593}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="25"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-A046-4231-AA1F-6FF7094856B6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:trendline>
             <c:spPr>
@@ -2441,9 +2545,9 @@
           </c:trendline>
           <c:cat>
             <c:strRef>
-              <c:f>USD!$A$2:$A$26</c:f>
+              <c:f>USD!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>10/11/2025</c:v>
                 </c:pt>
@@ -2518,16 +2622,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>4/28/2026</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5/5/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>USD!$D$2:$D$26</c:f>
+              <c:f>USD!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>-15627</c:v>
                 </c:pt>
@@ -2602,6 +2709,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>4508</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6259,6 +6369,145 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>AUD!$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5/5/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>AUD!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Position (Longs - Shorts)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>AUD!$D$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>78674</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6A63-4613-9352-805D76BBC0D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
@@ -8787,6 +9036,102 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000018-B37A-4820-896C-AC4DDFD9C9AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>CHF!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5/5/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>CHF!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Position (Longs - Shorts)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>CHF!$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-34521</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C764-4078-9A44-E178CD953A05}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9113,10 +9458,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>GBP!$D$2:$D$26</c:f>
+              <c:f>GBP!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>-81004</c:v>
                 </c:pt>
@@ -9191,6 +9536,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-60639</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-63908</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9224,12 +9572,12 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>GBP!$A$2:$A$26</c15:sqref>
+                          <c15:sqref>GBP!$A$2:$A$27</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="25"/>
+                      <c:ptCount val="26"/>
                       <c:pt idx="0">
                         <c:v>10/11/2025</c:v>
                       </c:pt>
@@ -9304,6 +9652,9 @@
                       </c:pt>
                       <c:pt idx="24">
                         <c:v>4/28/2026</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>5/5/2026</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -10910,6 +11261,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-8440-4BA9-8CAD-7E04214EE546}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -10964,6 +11320,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-8440-4BA9-8CAD-7E04214EE546}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
@@ -11018,6 +11379,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-8440-4BA9-8CAD-7E04214EE546}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
@@ -11072,6 +11438,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-8440-4BA9-8CAD-7E04214EE546}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
@@ -11129,6 +11500,73 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-8440-4BA9-8CAD-7E04214EE546}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="25"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-1D81-40FD-B1F9-FDFA1A041699}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:trendline>
             <c:spPr>
@@ -11145,9 +11583,9 @@
           </c:trendline>
           <c:cat>
             <c:strRef>
-              <c:f>JPY!$A$2:$A$26</c:f>
+              <c:f>JPY!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>10/11/2025</c:v>
                 </c:pt>
@@ -11222,16 +11660,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>4/28/2026</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5/5/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>JPY!$D$2:$D$26</c:f>
+              <c:f>JPY!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>48476</c:v>
                 </c:pt>
@@ -11306,6 +11747,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-102059</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-61738</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14717,6 +15161,136 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>CAD!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5/5/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="narHorz">
+              <a:fgClr>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:innerShdw blurRad="114300">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>CAD!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Position (Longs - Shorts)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>CAD!$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-14659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9234-4354-BCDC-96CDCB8B4331}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
@@ -15016,19 +15590,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:f>NZD!$D$1</c:f>
@@ -18685,6 +19246,176 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000019-7D69-487E-A2B3-0F4BCABC4FE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>NZD!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5/5/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:strRef>
+              <c:f>NZD!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Position (Longs - Shorts)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>NZD!$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-48251</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B035-431A-A20D-777DA2E5E6FC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19182,7 +19913,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="215">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -19193,7 +19924,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -19206,28 +19937,28 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="bg1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
@@ -19258,15 +19989,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -19275,73 +20014,60 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="70000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
   <cs:dataPointMarkerLayout symbol="circle" size="6"/>
@@ -19349,10 +20075,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -19374,13 +20100,15 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -19395,8 +20123,8 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
@@ -19414,10 +20142,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -19433,10 +20161,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
@@ -19452,7 +20180,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -19460,7 +20188,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -19473,38 +20220,20 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -19516,16 +20245,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -19539,22 +20269,22 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -19567,6 +20297,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -19574,10 +20315,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -19592,13 +20333,13 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="major">
+    <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="0" i="0" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -19607,10 +20348,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="15875" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -19643,8 +20384,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -19660,14 +20401,14 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -23757,17 +24498,17 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="28" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="15" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="50" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="29" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
@@ -23776,7 +24517,7 @@
       <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -23790,7 +24531,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45941</v>
       </c>
       <c r="B2" s="1">
@@ -23799,8 +24540,8 @@
       <c r="C2" s="1">
         <v>162331</v>
       </c>
-      <c r="D2" s="49">
-        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
+      <c r="D2" s="28">
+        <f t="shared" ref="D2:D28" si="0">B2-C2</f>
         <v>73589</v>
       </c>
       <c r="E2" s="1">
@@ -23810,12 +24551,12 @@
         <v>1584</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G27" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G28" si="1">E2-F2</f>
         <v>-18206</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
@@ -23824,7 +24565,7 @@
       <c r="C3" s="1">
         <v>144954</v>
       </c>
-      <c r="D3" s="49">
+      <c r="D3" s="28">
         <f t="shared" si="0"/>
         <v>99007</v>
       </c>
@@ -23840,7 +24581,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1">
@@ -23849,7 +24590,7 @@
       <c r="C4" s="1">
         <v>150321</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="28">
         <f t="shared" si="0"/>
         <v>94071</v>
       </c>
@@ -23865,7 +24606,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45700</v>
       </c>
       <c r="B5" s="1">
@@ -23874,7 +24615,7 @@
       <c r="C5" s="1">
         <v>141219</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="28">
         <f t="shared" si="0"/>
         <v>108453</v>
       </c>
@@ -23890,7 +24631,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>45912</v>
       </c>
       <c r="B6" s="1">
@@ -23899,7 +24640,7 @@
       <c r="C6" s="1">
         <v>129330</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="28">
         <f t="shared" si="0"/>
         <v>138788</v>
       </c>
@@ -23915,7 +24656,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1">
@@ -23924,7 +24665,7 @@
       <c r="C7" s="1">
         <v>132099</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="28">
         <f t="shared" si="0"/>
         <v>144903</v>
       </c>
@@ -23940,7 +24681,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1">
@@ -23949,7 +24690,7 @@
       <c r="C8" s="1">
         <v>133288</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="28">
         <f t="shared" si="0"/>
         <v>159891</v>
       </c>
@@ -23965,7 +24706,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1">
@@ -23974,7 +24715,7 @@
       <c r="C9" s="1">
         <v>137273</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="28">
         <f t="shared" si="0"/>
         <v>157465</v>
       </c>
@@ -23990,7 +24731,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46174</v>
       </c>
       <c r="B10" s="1">
@@ -23999,7 +24740,7 @@
       <c r="C10" s="1">
         <v>135441</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="28">
         <f t="shared" si="0"/>
         <v>162812</v>
       </c>
@@ -24015,7 +24756,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
@@ -24024,7 +24765,7 @@
       <c r="C11" s="1">
         <v>150936</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="28">
         <f t="shared" si="0"/>
         <v>132656</v>
       </c>
@@ -24040,7 +24781,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1">
@@ -24049,7 +24790,7 @@
       <c r="C12" s="1">
         <v>163540</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="28">
         <f t="shared" si="0"/>
         <v>111695</v>
       </c>
@@ -24065,7 +24806,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1">
@@ -24074,7 +24815,7 @@
       <c r="C13" s="1">
         <v>158202</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="28">
         <f t="shared" si="0"/>
         <v>132134</v>
       </c>
@@ -24090,7 +24831,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46083</v>
       </c>
       <c r="B14" s="1">
@@ -24099,7 +24840,7 @@
       <c r="C14" s="1">
         <v>138940</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="28">
         <f t="shared" si="0"/>
         <v>163361</v>
       </c>
@@ -24115,7 +24856,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46297</v>
       </c>
       <c r="B15" s="1">
@@ -24124,7 +24865,7 @@
       <c r="C15" s="1">
         <v>138399</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="28">
         <f t="shared" si="0"/>
         <v>180305</v>
       </c>
@@ -24140,7 +24881,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -24149,7 +24890,7 @@
       <c r="C16" s="1">
         <v>137069</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="28">
         <f t="shared" si="0"/>
         <v>174480</v>
       </c>
@@ -24165,7 +24906,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="21" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -24174,7 +24915,7 @@
       <c r="C17" s="1">
         <v>138017</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="28">
         <f t="shared" si="0"/>
         <v>156856</v>
       </c>
@@ -24190,7 +24931,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="1">
@@ -24199,7 +24940,7 @@
       <c r="C18" s="1">
         <v>158088</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="28">
         <f t="shared" si="0"/>
         <v>136498</v>
       </c>
@@ -24215,7 +24956,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46298</v>
       </c>
       <c r="B19" s="1">
@@ -24224,7 +24965,7 @@
       <c r="C19" s="1">
         <v>160542</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="28">
         <f t="shared" si="0"/>
         <v>105144</v>
       </c>
@@ -24240,7 +24981,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -24249,7 +24990,7 @@
       <c r="C20" s="1">
         <v>191754</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="28">
         <f t="shared" si="0"/>
         <v>21132</v>
       </c>
@@ -24265,7 +25006,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="3">
@@ -24274,14 +25015,14 @@
       <c r="C21" s="3">
         <v>190746</v>
       </c>
-      <c r="D21" s="49">
+      <c r="D21" s="28">
         <f t="shared" si="0"/>
         <v>9279</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="3">
         <v>-12861</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="3">
         <v>-1008</v>
       </c>
       <c r="G21" s="1">
@@ -24290,157 +25031,182 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="1">
         <v>200168</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="1">
         <v>199661</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="28">
         <f t="shared" si="0"/>
         <v>507</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="1">
         <v>143</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="1">
         <v>8915</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="1">
         <f t="shared" si="1"/>
         <v>-8772</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>200946</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>208487</v>
       </c>
-      <c r="D23" s="50">
+      <c r="D23" s="28">
         <f t="shared" si="0"/>
         <v>-7541</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>778</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>8826</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="1">
         <f t="shared" si="1"/>
         <v>-8048</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="48">
+      <c r="A24" s="37">
         <v>46126</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>129517</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>64442</v>
       </c>
-      <c r="D24" s="50">
+      <c r="D24" s="28">
         <f t="shared" si="0"/>
         <v>65075</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>-8442</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>-2704</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="1">
         <f t="shared" si="1"/>
         <v>-5738</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46126</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>214639</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>188621</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="28">
         <f t="shared" si="0"/>
         <v>26018</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>13693</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>-19866</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="1">
         <f t="shared" si="1"/>
         <v>33559</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46133</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>217407</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>176083</v>
       </c>
-      <c r="D26" s="50">
+      <c r="D26" s="28">
         <f t="shared" si="0"/>
         <v>41324</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>2768</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>-12538</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="1">
         <f t="shared" si="1"/>
         <v>15306</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
+      <c r="A27" s="13">
         <v>46140</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="3">
         <v>217091</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>181379</v>
       </c>
-      <c r="D27" s="50">
+      <c r="D27" s="28">
         <f t="shared" si="0"/>
         <v>35712</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>-316</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="3">
         <v>5296</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="1">
         <f t="shared" si="1"/>
         <v>-5612</v>
       </c>
     </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B28" s="3">
+        <v>217474</v>
+      </c>
+      <c r="C28" s="3">
+        <v>185272</v>
+      </c>
+      <c r="D28" s="28">
+        <f t="shared" si="0"/>
+        <v>32202</v>
+      </c>
+      <c r="E28" s="3">
+        <v>383</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3893</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="1"/>
+        <v>-3510</v>
+      </c>
+    </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F29" s="35"/>
+      <c r="F29" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -24451,7 +25217,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB577F0-051C-45DD-9491-CB7C4AFFE320}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -24487,7 +25253,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="A2" s="11">
         <v>46140</v>
       </c>
       <c r="B2" s="7">
@@ -24509,6 +25275,31 @@
       <c r="G2">
         <f>E2-F2</f>
         <v>321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>46147</v>
+      </c>
+      <c r="B3">
+        <v>19301</v>
+      </c>
+      <c r="C3">
+        <v>17860</v>
+      </c>
+      <c r="D3" s="7">
+        <f>B3-C3</f>
+        <v>1441</v>
+      </c>
+      <c r="E3">
+        <v>1870</v>
+      </c>
+      <c r="F3">
+        <v>2821</v>
+      </c>
+      <c r="G3">
+        <f>E3-F3</f>
+        <v>-951</v>
       </c>
     </row>
   </sheetData>
@@ -24518,20 +25309,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E049AD9-8C60-4A1C-9327-32192CC888AD}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="28" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="24" customWidth="1"/>
+    <col min="1" max="1" width="16" style="15" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="25" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="9" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
@@ -24540,7 +25331,7 @@
       <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -24554,17 +25345,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45941</v>
       </c>
-      <c r="B2" s="51">
+      <c r="B2" s="1">
         <v>16004</v>
       </c>
       <c r="C2" s="1">
         <v>31631</v>
       </c>
-      <c r="D2" s="53">
-        <f t="shared" ref="D2:D26" si="0">B2-C2</f>
+      <c r="D2" s="30">
+        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
         <v>-15627</v>
       </c>
       <c r="E2" s="1">
@@ -24574,21 +25365,21 @@
         <v>-576</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G26" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G27" si="1">E2-F2</f>
         <v>-65</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="1">
         <v>16893</v>
       </c>
       <c r="C3" s="1">
         <v>33001</v>
       </c>
-      <c r="D3" s="53">
+      <c r="D3" s="30">
         <f t="shared" si="0"/>
         <v>-16108</v>
       </c>
@@ -24604,16 +25395,16 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="51">
+      <c r="B4" s="1">
         <v>18448</v>
       </c>
       <c r="C4" s="1">
         <v>34795</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="30">
         <f t="shared" si="0"/>
         <v>-16347</v>
       </c>
@@ -24629,16 +25420,16 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45700</v>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="1">
         <v>14444</v>
       </c>
       <c r="C5" s="1">
         <v>30662</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="30">
         <f t="shared" si="0"/>
         <v>-16218</v>
       </c>
@@ -24654,16 +25445,16 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>45912</v>
       </c>
-      <c r="B6" s="51">
+      <c r="B6" s="1">
         <v>14778</v>
       </c>
       <c r="C6" s="1">
         <v>28652</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>-13874</v>
       </c>
@@ -24679,16 +25470,16 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="51">
+      <c r="B7" s="1">
         <v>15895</v>
       </c>
       <c r="C7" s="1">
         <v>20490</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="30">
         <f t="shared" si="0"/>
         <v>-4595</v>
       </c>
@@ -24704,16 +25495,16 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="51">
+      <c r="B8" s="1">
         <v>16688</v>
       </c>
       <c r="C8" s="1">
         <v>20709</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="30">
         <f t="shared" si="0"/>
         <v>-4021</v>
       </c>
@@ -24729,16 +25520,16 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="51">
+      <c r="B9" s="1">
         <v>16652</v>
       </c>
       <c r="C9" s="1">
         <v>20612</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="30">
         <f t="shared" si="0"/>
         <v>-3960</v>
       </c>
@@ -24754,16 +25545,16 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46174</v>
       </c>
-      <c r="B10" s="51">
+      <c r="B10" s="1">
         <v>17671</v>
       </c>
       <c r="C10" s="1">
         <v>21502</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="30">
         <f t="shared" si="0"/>
         <v>-3831</v>
       </c>
@@ -24779,16 +25570,16 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="51">
+      <c r="B11" s="1">
         <v>17929</v>
       </c>
       <c r="C11" s="1">
         <v>21659</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="30">
         <f t="shared" si="0"/>
         <v>-3730</v>
       </c>
@@ -24804,16 +25595,16 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="1">
         <v>16003</v>
       </c>
       <c r="C12" s="1">
         <v>22421</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="30">
         <f t="shared" si="0"/>
         <v>-6418</v>
       </c>
@@ -24829,16 +25620,16 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="1">
         <v>17945</v>
       </c>
       <c r="C13" s="1">
         <v>22350</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="30">
         <f t="shared" si="0"/>
         <v>-4405</v>
       </c>
@@ -24854,16 +25645,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46083</v>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="1">
         <v>16610</v>
       </c>
       <c r="C14" s="1">
         <v>17462</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="30">
         <f t="shared" si="0"/>
         <v>-852</v>
       </c>
@@ -24879,16 +25670,16 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46297</v>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="1">
         <v>16131</v>
       </c>
       <c r="C15" s="1">
         <v>16860</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="30">
         <f t="shared" si="0"/>
         <v>-729</v>
       </c>
@@ -24904,16 +25695,16 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="51">
+      <c r="B16" s="1">
         <v>15416</v>
       </c>
       <c r="C16" s="1">
         <v>15088</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="30">
         <f t="shared" si="0"/>
         <v>328</v>
       </c>
@@ -24929,16 +25720,16 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="1">
         <v>13295</v>
       </c>
       <c r="C17" s="1">
         <v>15084</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="30">
         <f t="shared" si="0"/>
         <v>-1789</v>
       </c>
@@ -24954,16 +25745,16 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
-      <c r="B18" s="51">
+      <c r="B18" s="1">
         <v>15061</v>
       </c>
       <c r="C18" s="1">
         <v>20050</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="30">
         <f t="shared" si="0"/>
         <v>-4989</v>
       </c>
@@ -24979,16 +25770,16 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46298</v>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="1">
         <v>16384</v>
       </c>
       <c r="C19" s="1">
         <v>22266</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="30">
         <f t="shared" si="0"/>
         <v>-5882</v>
       </c>
@@ -25004,16 +25795,16 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="51">
+      <c r="B20" s="1">
         <v>21426</v>
       </c>
       <c r="C20" s="1">
         <v>17733</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="30">
         <f t="shared" si="0"/>
         <v>3693</v>
       </c>
@@ -25029,16 +25820,16 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="3">
         <v>20457</v>
       </c>
       <c r="C21" s="3">
         <v>16840</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="30">
         <f t="shared" si="0"/>
         <v>3617</v>
       </c>
@@ -25054,128 +25845,153 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="52">
+      <c r="B22" s="1">
         <v>21708</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="1">
         <v>18027</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="30">
         <f t="shared" si="0"/>
         <v>3681</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="1">
         <v>1251</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="1">
         <v>1187</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="1">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="3">
         <v>23084</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>17573</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="30">
         <f t="shared" si="0"/>
         <v>5511</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>1376</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>-454</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="1">
         <f t="shared" si="1"/>
         <v>1830</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="13">
         <v>46126</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="3">
         <v>18970</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>13800</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="30">
         <f t="shared" si="0"/>
         <v>5170</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>-4114</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>-3773</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="1">
         <f t="shared" si="1"/>
         <v>-341</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46133</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="3">
         <v>17617</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>12634</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="30">
         <f t="shared" si="0"/>
         <v>4983</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>-1353</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>-1166</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="1">
         <f t="shared" si="1"/>
         <v>-187</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46140</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="3">
         <v>17180</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>12672</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="30">
         <f t="shared" si="0"/>
         <v>4508</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>-437</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>38</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="1">
         <f t="shared" si="1"/>
         <v>-475</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>17048</v>
+      </c>
+      <c r="C27" s="3">
+        <v>16355</v>
+      </c>
+      <c r="D27" s="30">
+        <f t="shared" si="0"/>
+        <v>693</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-132</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3683</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="1"/>
+        <v>-3815</v>
       </c>
     </row>
   </sheetData>
@@ -25187,20 +26003,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A64D1E-BA3D-43E2-BF69-69E226E6EEE7}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="14" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" style="25" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -25209,7 +26025,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -25218,12 +26034,12 @@
       <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45971</v>
       </c>
       <c r="B2" s="3">
@@ -25232,7 +26048,7 @@
       <c r="C2" s="3">
         <v>121741</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="24">
         <f>B2-C2</f>
         <v>-78627</v>
       </c>
@@ -25242,13 +26058,13 @@
       <c r="F2" s="1">
         <v>-195</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="32">
         <f>E2-F2</f>
         <v>-7051</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="13">
         <v>45979</v>
       </c>
       <c r="B3" s="3">
@@ -25257,8 +26073,8 @@
       <c r="C3" s="3">
         <v>121577</v>
       </c>
-      <c r="D3" s="53">
-        <f t="shared" ref="D3:D25" si="0">B3-C3</f>
+      <c r="D3" s="30">
+        <f t="shared" ref="D3:D27" si="0">B3-C3</f>
         <v>-75856</v>
       </c>
       <c r="E3" s="3">
@@ -25267,13 +26083,13 @@
       <c r="F3" s="1">
         <v>-164</v>
       </c>
-      <c r="G3" s="1">
-        <f t="shared" ref="G3:G25" si="1">E3-F3</f>
+      <c r="G3" s="32">
+        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
         <v>2771</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
+      <c r="A4" s="13">
         <v>45986</v>
       </c>
       <c r="B4" s="3">
@@ -25282,7 +26098,7 @@
       <c r="C4" s="3">
         <v>128094</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="30">
         <f t="shared" si="0"/>
         <v>-84176</v>
       </c>
@@ -25292,13 +26108,13 @@
       <c r="F4" s="3">
         <v>6517</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="32">
         <f t="shared" si="1"/>
         <v>-8320</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45993</v>
       </c>
       <c r="B5" s="3">
@@ -25307,7 +26123,7 @@
       <c r="C5" s="3">
         <v>129261</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="30">
         <f t="shared" si="0"/>
         <v>-83393</v>
       </c>
@@ -25317,13 +26133,13 @@
       <c r="F5" s="3">
         <v>1167</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="32">
         <f t="shared" si="1"/>
         <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>46000</v>
       </c>
       <c r="B6" s="3">
@@ -25332,7 +26148,7 @@
       <c r="C6" s="3">
         <v>120516</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>-62947</v>
       </c>
@@ -25342,13 +26158,13 @@
       <c r="F6" s="3">
         <v>-8745</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="32">
         <f t="shared" si="1"/>
         <v>20446</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="13">
         <v>46007</v>
       </c>
       <c r="B7" s="3">
@@ -25357,7 +26173,7 @@
       <c r="C7" s="3">
         <v>89535</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="30">
         <f t="shared" si="0"/>
         <v>-21895</v>
       </c>
@@ -25367,13 +26183,13 @@
       <c r="F7" s="3">
         <v>-30981</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="32">
         <f t="shared" si="1"/>
         <v>41052</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="13">
         <v>46014</v>
       </c>
       <c r="B8" s="3">
@@ -25382,7 +26198,7 @@
       <c r="C8" s="3">
         <v>92255</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="30">
         <f t="shared" si="0"/>
         <v>-21598</v>
       </c>
@@ -25392,13 +26208,13 @@
       <c r="F8" s="3">
         <v>2720</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="32">
         <f t="shared" si="1"/>
         <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="13">
         <v>46021</v>
       </c>
       <c r="B9" s="3">
@@ -25407,7 +26223,7 @@
       <c r="C9" s="3">
         <v>98713</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="30">
         <f t="shared" si="0"/>
         <v>-21216</v>
       </c>
@@ -25417,13 +26233,13 @@
       <c r="F9" s="3">
         <v>6458</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="32">
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46028</v>
       </c>
       <c r="B10" s="3">
@@ -25432,7 +26248,7 @@
       <c r="C10" s="3">
         <v>99451</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="30">
         <f t="shared" si="0"/>
         <v>-18960</v>
       </c>
@@ -25442,13 +26258,13 @@
       <c r="F10" s="1">
         <v>738</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="32">
         <f t="shared" si="1"/>
         <v>2256</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="13">
         <v>46035</v>
       </c>
       <c r="B11" s="3">
@@ -25457,7 +26273,7 @@
       <c r="C11" s="3">
         <v>102801</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="30">
         <f t="shared" si="0"/>
         <v>-18846</v>
       </c>
@@ -25467,13 +26283,13 @@
       <c r="F11" s="3">
         <v>3350</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="32">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+      <c r="A12" s="13">
         <v>46042</v>
       </c>
       <c r="B12" s="3">
@@ -25482,7 +26298,7 @@
       <c r="C12" s="3">
         <v>99770</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="30">
         <f t="shared" si="0"/>
         <v>-14011</v>
       </c>
@@ -25492,13 +26308,13 @@
       <c r="F12" s="3">
         <v>-3031</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="32">
         <f t="shared" si="1"/>
         <v>4835</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="13">
         <v>46049</v>
       </c>
       <c r="B13" s="3">
@@ -25507,7 +26323,7 @@
       <c r="C13" s="3">
         <v>102660</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="30">
         <f t="shared" si="0"/>
         <v>7146</v>
       </c>
@@ -25517,13 +26333,13 @@
       <c r="F13" s="3">
         <v>2890</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="32">
         <f t="shared" si="1"/>
         <v>21157</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46056</v>
       </c>
       <c r="B14" s="3">
@@ -25532,7 +26348,7 @@
       <c r="C14" s="3">
         <v>92633</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="30">
         <f t="shared" si="0"/>
         <v>26118</v>
       </c>
@@ -25542,13 +26358,13 @@
       <c r="F14" s="3">
         <v>-10027</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="32">
         <f t="shared" si="1"/>
         <v>18972</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46063</v>
       </c>
       <c r="B15" s="3">
@@ -25557,7 +26373,7 @@
       <c r="C15" s="3">
         <v>79557</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="30">
         <f t="shared" si="0"/>
         <v>33209</v>
       </c>
@@ -25567,13 +26383,13 @@
       <c r="F15" s="3">
         <v>-13076</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="32">
         <f t="shared" si="1"/>
         <v>7091</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
+      <c r="A16" s="13">
         <v>46070</v>
       </c>
       <c r="B16" s="3">
@@ -25582,7 +26398,7 @@
       <c r="C16" s="3">
         <v>71889</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="30">
         <f t="shared" si="0"/>
         <v>45931</v>
       </c>
@@ -25592,13 +26408,13 @@
       <c r="F16" s="3">
         <v>-7668</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="32">
         <f t="shared" si="1"/>
         <v>12722</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="13">
         <v>46077</v>
       </c>
       <c r="B17" s="3">
@@ -25607,7 +26423,7 @@
       <c r="C17" s="3">
         <v>69017</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="30">
         <f t="shared" si="0"/>
         <v>52644</v>
       </c>
@@ -25617,13 +26433,13 @@
       <c r="F17" s="3">
         <v>-2872</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="32">
         <f t="shared" si="1"/>
         <v>6713</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="3">
@@ -25632,7 +26448,7 @@
       <c r="C18" s="3">
         <v>68753</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="30">
         <f t="shared" si="0"/>
         <v>67762</v>
       </c>
@@ -25642,13 +26458,13 @@
       <c r="F18" s="1">
         <v>-264</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="32">
         <f t="shared" si="1"/>
         <v>15118</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46091</v>
       </c>
       <c r="B19" s="3">
@@ -25657,7 +26473,7 @@
       <c r="C19" s="3">
         <v>67197</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="30">
         <f t="shared" si="0"/>
         <v>54197</v>
       </c>
@@ -25667,13 +26483,13 @@
       <c r="F19" s="3">
         <v>-1556</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="32">
         <f t="shared" si="1"/>
         <v>-13565</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="13">
         <v>46098</v>
       </c>
       <c r="B20" s="3">
@@ -25682,7 +26498,7 @@
       <c r="C20" s="3">
         <v>67013</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="30">
         <f t="shared" si="0"/>
         <v>69061</v>
       </c>
@@ -25692,13 +26508,13 @@
       <c r="F20" s="1">
         <v>-184</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="32">
         <f t="shared" si="1"/>
         <v>14864</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="13">
         <v>46105</v>
       </c>
       <c r="B21" s="3">
@@ -25707,7 +26523,7 @@
       <c r="C21" s="3">
         <v>61757</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="30">
         <f t="shared" si="0"/>
         <v>70872</v>
       </c>
@@ -25717,110 +26533,151 @@
       <c r="F21" s="3">
         <v>-5256</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="32">
         <f t="shared" si="1"/>
         <v>1811</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
+      <c r="A22" s="13">
         <v>46112</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="3">
         <v>141775</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="3">
         <v>60269</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="30">
         <f t="shared" si="0"/>
         <v>81506</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="3">
         <v>9146</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="1">
         <v>1488</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="32">
         <f t="shared" si="1"/>
         <v>7658</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>137959</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>67146</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="30">
         <f t="shared" si="0"/>
         <v>70813</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>-3816</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>6877</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="32">
         <f t="shared" si="1"/>
         <v>-10693</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="13">
         <v>46133</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>128811</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>63994</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="30">
         <f t="shared" si="0"/>
         <v>64817</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>-706</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>-448</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="32">
         <f t="shared" si="1"/>
         <v>-258</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46140</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>136909</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>65040</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="30">
         <f t="shared" si="0"/>
         <v>71869</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>8098</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>1046</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="32">
         <f t="shared" si="1"/>
         <v>7052</v>
       </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B26" s="3">
+        <v>143214</v>
+      </c>
+      <c r="C26" s="3">
+        <v>64540</v>
+      </c>
+      <c r="D26" s="30">
+        <f t="shared" si="0"/>
+        <v>78674</v>
+      </c>
+      <c r="E26" s="3">
+        <v>6305</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G26" s="32">
+        <f t="shared" si="1"/>
+        <v>6805</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="45">
+        <v>46154</v>
+      </c>
+      <c r="B27" s="46">
+        <v>150800</v>
+      </c>
+      <c r="C27" s="46">
+        <v>65810</v>
+      </c>
+      <c r="D27" s="30">
+        <f t="shared" si="0"/>
+        <v>84990</v>
+      </c>
+      <c r="E27" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25830,29 +26687,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484D440D-6E6B-4B12-86E6-BEF7B583A71E}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="28" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="15" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -25866,16 +26723,16 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45971</v>
       </c>
       <c r="B2" s="3">
         <v>7403</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="3">
         <v>43452</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="34">
         <f>B2-C2</f>
         <v>-36049</v>
       </c>
@@ -25891,17 +26748,17 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="13">
         <v>45979</v>
       </c>
       <c r="B3" s="3">
         <v>8746</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="3">
         <v>40931</v>
       </c>
-      <c r="D3" s="11">
-        <f t="shared" ref="D3:D26" si="0">B3-C3</f>
+      <c r="D3" s="34">
+        <f t="shared" ref="D3:D27" si="0">B3-C3</f>
         <v>-32185</v>
       </c>
       <c r="E3" s="3">
@@ -25911,21 +26768,21 @@
         <v>-2521</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G27" si="1">E3-F3</f>
         <v>3864</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
+      <c r="A4" s="13">
         <v>45986</v>
       </c>
       <c r="B4" s="3">
         <v>7571</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="3">
         <v>42931</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="34">
         <f t="shared" si="0"/>
         <v>-35360</v>
       </c>
@@ -25941,16 +26798,16 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45993</v>
       </c>
       <c r="B5" s="3">
         <v>6894</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="3">
         <v>42679</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="34">
         <f t="shared" si="0"/>
         <v>-35785</v>
       </c>
@@ -25966,16 +26823,16 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>46000</v>
       </c>
       <c r="B6" s="3">
         <v>8456</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="3">
         <v>47059</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="34">
         <f t="shared" si="0"/>
         <v>-38603</v>
       </c>
@@ -25991,16 +26848,16 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="13">
         <v>46007</v>
       </c>
       <c r="B7" s="3">
         <v>9448</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="3">
         <v>48355</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="34">
         <f t="shared" si="0"/>
         <v>-38907</v>
       </c>
@@ -26016,16 +26873,16 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="13">
         <v>46014</v>
       </c>
       <c r="B8" s="3">
         <v>8780</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="3">
         <v>52769</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="34">
         <f t="shared" si="0"/>
         <v>-43989</v>
       </c>
@@ -26041,16 +26898,16 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="13">
         <v>46021</v>
       </c>
       <c r="B9" s="3">
         <v>8910</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="3">
         <v>53108</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="34">
         <f t="shared" si="0"/>
         <v>-44198</v>
       </c>
@@ -26066,16 +26923,16 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46028</v>
       </c>
       <c r="B10" s="3">
         <v>11077</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="3">
         <v>51343</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="34">
         <f t="shared" si="0"/>
         <v>-40266</v>
       </c>
@@ -26091,16 +26948,16 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="13">
         <v>46035</v>
       </c>
       <c r="B11" s="3">
         <v>13395</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="3">
         <v>56787</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="34">
         <f t="shared" si="0"/>
         <v>-43392</v>
       </c>
@@ -26116,16 +26973,16 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+      <c r="A12" s="13">
         <v>46042</v>
       </c>
       <c r="B12" s="3">
         <v>12257</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="3">
         <v>55464</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="35">
         <f>B12-C12</f>
         <v>-43207</v>
       </c>
@@ -26141,16 +26998,16 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="13">
         <v>46049</v>
       </c>
       <c r="B13" s="3">
         <v>9724</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="3">
         <v>52617</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="35">
         <f>B13-C13</f>
         <v>-42893</v>
       </c>
@@ -26166,16 +27023,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46056</v>
       </c>
       <c r="B14" s="3">
         <v>9687</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="3">
         <v>50404</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="34">
         <f t="shared" si="0"/>
         <v>-40717</v>
       </c>
@@ -26191,16 +27048,16 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46063</v>
       </c>
       <c r="B15" s="3">
         <v>9600</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="3">
         <v>51859</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="34">
         <f t="shared" si="0"/>
         <v>-42259</v>
       </c>
@@ -26216,16 +27073,16 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
+      <c r="A16" s="13">
         <v>46070</v>
       </c>
       <c r="B16" s="3">
         <v>10072</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="3">
         <v>50953</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="35">
         <f>B16-C16</f>
         <v>-40881</v>
       </c>
@@ -26241,16 +27098,16 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="13">
         <v>46077</v>
       </c>
       <c r="B17" s="3">
         <v>11525</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="3">
         <v>52711</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="34">
         <f t="shared" si="0"/>
         <v>-41186</v>
       </c>
@@ -26266,16 +27123,16 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="3">
         <v>12390</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="3">
         <v>53673</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="34">
         <f t="shared" si="0"/>
         <v>-41283</v>
       </c>
@@ -26291,16 +27148,16 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46091</v>
       </c>
       <c r="B19" s="3">
         <v>12152</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="3">
         <v>53244</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="34">
         <f t="shared" si="0"/>
         <v>-41092</v>
       </c>
@@ -26316,16 +27173,16 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="13">
         <v>46098</v>
       </c>
       <c r="B20" s="3">
         <v>8175</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="3">
         <v>33388</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="34">
         <f t="shared" si="0"/>
         <v>-25213</v>
       </c>
@@ -26341,16 +27198,16 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="13">
         <v>46105</v>
       </c>
       <c r="B21" s="3">
         <v>7831</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="3">
         <v>34928</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="34">
         <f t="shared" si="0"/>
         <v>-27097</v>
       </c>
@@ -26366,128 +27223,158 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
+      <c r="A22" s="13">
         <v>46112</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="3">
         <v>9315</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="3">
         <v>39186</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="34">
         <f t="shared" si="0"/>
         <v>-29871</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="1">
         <v>1484</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="3">
         <v>4258</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="1">
         <f t="shared" si="1"/>
         <v>-2774</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>10586</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="3">
         <v>41280</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="34">
         <f t="shared" si="0"/>
         <v>-30694</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>1271</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>2094</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="1">
         <f t="shared" si="1"/>
         <v>-823</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="13">
         <v>46126</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>9637</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="3">
         <v>43734</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="34">
         <f t="shared" si="0"/>
         <v>-34097</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>-949</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>2454</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="1">
         <f t="shared" si="1"/>
         <v>-3403</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46133</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>8372</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="3">
         <v>41645</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="34">
         <f t="shared" si="0"/>
         <v>-33273</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>-1265</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>-2089</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="1">
         <f t="shared" si="1"/>
         <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>6359</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="3">
         <v>41580</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="34">
         <f t="shared" si="0"/>
         <v>-35221</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>-2013</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>-65</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="1">
         <f t="shared" si="1"/>
         <v>-1948</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>7145</v>
+      </c>
+      <c r="C27" s="3">
+        <v>41666</v>
+      </c>
+      <c r="D27" s="38">
+        <f t="shared" si="0"/>
+        <v>-34521</v>
+      </c>
+      <c r="E27" s="3">
+        <v>786</v>
+      </c>
+      <c r="F27" s="3">
+        <v>86</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -26498,20 +27385,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E55D1F-7511-410A-9BDB-6D70A2FC177B}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" style="15" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="41" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="23" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -26520,7 +27407,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -26534,7 +27421,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45941</v>
       </c>
       <c r="B2" s="1">
@@ -26543,8 +27430,8 @@
       <c r="C2" s="1">
         <v>133427</v>
       </c>
-      <c r="D2" s="40">
-        <f t="shared" ref="D2:D26" si="0">B2-C2</f>
+      <c r="D2" s="22">
+        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
         <v>-81004</v>
       </c>
       <c r="E2" s="1">
@@ -26559,7 +27446,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
@@ -26568,7 +27455,7 @@
       <c r="C3" s="1">
         <v>132446</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="22">
         <f t="shared" si="0"/>
         <v>-79257</v>
       </c>
@@ -26584,7 +27471,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1">
@@ -26593,7 +27480,7 @@
       <c r="C4" s="1">
         <v>138478</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="22">
         <f t="shared" si="0"/>
         <v>-93221</v>
       </c>
@@ -26609,7 +27496,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45700</v>
       </c>
       <c r="B5" s="1">
@@ -26618,7 +27505,7 @@
       <c r="C5" s="1">
         <v>132432</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="22">
         <f t="shared" si="0"/>
         <v>-80180</v>
       </c>
@@ -26634,7 +27521,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>45912</v>
       </c>
       <c r="B6" s="1">
@@ -26643,7 +27530,7 @@
       <c r="C6" s="1">
         <v>135834</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="22">
         <f t="shared" si="0"/>
         <v>-75515</v>
       </c>
@@ -26659,7 +27546,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1">
@@ -26668,7 +27555,7 @@
       <c r="C7" s="1">
         <v>110466</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>-48498</v>
       </c>
@@ -26684,7 +27571,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1">
@@ -26693,7 +27580,7 @@
       <c r="C8" s="1">
         <v>104739</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="22">
         <f t="shared" si="0"/>
         <v>-41199</v>
       </c>
@@ -26709,7 +27596,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1">
@@ -26718,7 +27605,7 @@
       <c r="C9" s="1">
         <v>102699</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="22">
         <f t="shared" si="0"/>
         <v>-33207</v>
       </c>
@@ -26734,7 +27621,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46174</v>
       </c>
       <c r="B10" s="1">
@@ -26743,7 +27630,7 @@
       <c r="C10" s="1">
         <v>107024</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="22">
         <f t="shared" si="0"/>
         <v>-30538</v>
       </c>
@@ -26759,7 +27646,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
@@ -26768,7 +27655,7 @@
       <c r="C11" s="1">
         <v>104273</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="22">
         <f t="shared" si="0"/>
         <v>-25270</v>
       </c>
@@ -26784,7 +27671,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1">
@@ -26793,7 +27680,7 @@
       <c r="C12" s="1">
         <v>103312</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="22">
         <f t="shared" si="0"/>
         <v>-21980</v>
       </c>
@@ -26809,7 +27696,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1">
@@ -26818,7 +27705,7 @@
       <c r="C13" s="1">
         <v>103948</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="22">
         <f t="shared" si="0"/>
         <v>-16162</v>
       </c>
@@ -26834,7 +27721,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46083</v>
       </c>
       <c r="B14" s="1">
@@ -26843,7 +27730,7 @@
       <c r="C14" s="1">
         <v>108804</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="22">
         <f t="shared" si="0"/>
         <v>-13911</v>
       </c>
@@ -26859,7 +27746,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46297</v>
       </c>
       <c r="B15" s="1">
@@ -26868,7 +27755,7 @@
       <c r="C15" s="1">
         <v>114183</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="22">
         <f t="shared" si="0"/>
         <v>-25810</v>
       </c>
@@ -26884,7 +27771,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -26893,7 +27780,7 @@
       <c r="C16" s="1">
         <v>124419</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="22">
         <f t="shared" si="0"/>
         <v>-42404</v>
       </c>
@@ -26909,7 +27796,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="21" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -26918,7 +27805,7 @@
       <c r="C17" s="1">
         <v>124285</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="22">
         <f t="shared" si="0"/>
         <v>-57072</v>
       </c>
@@ -26934,7 +27821,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="1">
@@ -26943,7 +27830,7 @@
       <c r="C18" s="1">
         <v>132185</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="22">
         <f t="shared" si="0"/>
         <v>-72686</v>
       </c>
@@ -26959,7 +27846,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46298</v>
       </c>
       <c r="B19" s="1">
@@ -26968,7 +27855,7 @@
       <c r="C19" s="1">
         <v>133467</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="22">
         <f t="shared" si="0"/>
         <v>-84197</v>
       </c>
@@ -26984,7 +27871,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -26993,7 +27880,7 @@
       <c r="C20" s="1">
         <v>109808</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="22">
         <f t="shared" si="0"/>
         <v>-65515</v>
       </c>
@@ -27004,12 +27891,12 @@
         <v>-23659</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" ref="G20:G26" si="2">E20-F20</f>
+        <f t="shared" ref="G20:G27" si="2">E20-F20</f>
         <v>18682</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="3">
@@ -27018,7 +27905,7 @@
       <c r="C21" s="3">
         <v>104881</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="22">
         <f t="shared" si="0"/>
         <v>-58422</v>
       </c>
@@ -27034,128 +27921,153 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="1">
         <v>51304</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="1">
         <v>103969</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="22">
         <f t="shared" si="0"/>
         <v>-52665</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="1">
         <v>4845</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="1">
         <v>912</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="1">
         <f t="shared" si="2"/>
         <v>3933</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>47344</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>103698</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="22">
         <f t="shared" si="0"/>
         <v>-56354</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>-3960</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>-271</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="1">
         <f t="shared" si="2"/>
         <v>-3689</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="13">
         <v>46126</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>54947</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>109671</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="22">
         <f t="shared" si="0"/>
         <v>-54724</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>7603</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>5973</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="1">
         <f t="shared" si="2"/>
         <v>1630</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46133</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>63086</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>115125</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="22">
         <f t="shared" si="0"/>
         <v>-52039</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>8139</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>5454</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="1">
         <f t="shared" si="2"/>
         <v>2685</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>59577</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>120216</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="22">
         <f t="shared" si="0"/>
         <v>-60639</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>-3509</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>5091</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="1">
         <f t="shared" si="2"/>
         <v>-8600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>62573</v>
+      </c>
+      <c r="C27" s="3">
+        <v>126481</v>
+      </c>
+      <c r="D27" s="22">
+        <f t="shared" si="0"/>
+        <v>-63908</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2996</v>
+      </c>
+      <c r="F27" s="3">
+        <v>6265</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="2"/>
+        <v>-3269</v>
       </c>
     </row>
   </sheetData>
@@ -27167,20 +28079,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8ECBF1-DFF0-4C27-BC6C-1C623368F16D}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="41" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" style="23" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -27189,7 +28101,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -27203,7 +28115,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45941</v>
       </c>
       <c r="B2" s="1">
@@ -27212,7 +28124,7 @@
       <c r="C2" s="1">
         <v>123873</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="22">
         <f t="shared" ref="D2:D20" si="0">B2-C2</f>
         <v>48476</v>
       </c>
@@ -27223,12 +28135,12 @@
         <v>4958</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G26" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G27" si="1">E2-F2</f>
         <v>-2789</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
@@ -27237,7 +28149,7 @@
       <c r="C3" s="1">
         <v>138733</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="22">
         <f t="shared" si="0"/>
         <v>31157</v>
       </c>
@@ -27253,7 +28165,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1">
@@ -27262,7 +28174,7 @@
       <c r="C4" s="1">
         <v>142701</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="22">
         <f t="shared" si="0"/>
         <v>26517</v>
       </c>
@@ -27278,7 +28190,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45700</v>
       </c>
       <c r="B5" s="1">
@@ -27287,7 +28199,7 @@
       <c r="C5" s="1">
         <v>148540</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="22">
         <f t="shared" si="0"/>
         <v>36418</v>
       </c>
@@ -27303,7 +28215,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>45912</v>
       </c>
       <c r="B6" s="1">
@@ -27312,7 +28224,7 @@
       <c r="C6" s="1">
         <v>167040</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="22">
         <f t="shared" si="0"/>
         <v>17448</v>
       </c>
@@ -27328,7 +28240,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1">
@@ -27337,7 +28249,7 @@
       <c r="C7" s="1">
         <v>149217</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>-2942</v>
       </c>
@@ -27353,7 +28265,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1">
@@ -27362,7 +28274,7 @@
       <c r="C8" s="1">
         <v>139910</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="22">
         <f t="shared" si="0"/>
         <v>1223</v>
       </c>
@@ -27378,7 +28290,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1">
@@ -27387,7 +28299,7 @@
       <c r="C9" s="1">
         <v>130528</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="22">
         <f t="shared" si="0"/>
         <v>14068</v>
       </c>
@@ -27403,7 +28315,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46174</v>
       </c>
       <c r="B10" s="1">
@@ -27412,7 +28324,7 @@
       <c r="C10" s="1">
         <v>131626</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="22">
         <f t="shared" si="0"/>
         <v>8815</v>
       </c>
@@ -27428,7 +28340,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
@@ -27437,7 +28349,7 @@
       <c r="C11" s="1">
         <v>156907</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="22">
         <f t="shared" si="0"/>
         <v>-45164</v>
       </c>
@@ -27453,7 +28365,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1">
@@ -27462,7 +28374,7 @@
       <c r="C12" s="1">
         <v>151968</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="22">
         <f t="shared" si="0"/>
         <v>-44829</v>
       </c>
@@ -27478,7 +28390,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1">
@@ -27487,7 +28399,7 @@
       <c r="C13" s="1">
         <v>138393</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="22">
         <f t="shared" si="0"/>
         <v>-33933</v>
       </c>
@@ -27503,7 +28415,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46083</v>
       </c>
       <c r="B14" s="1">
@@ -27512,7 +28424,7 @@
       <c r="C14" s="1">
         <v>133650</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="22">
         <f t="shared" si="0"/>
         <v>-19222</v>
       </c>
@@ -27528,7 +28440,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46297</v>
       </c>
       <c r="B15" s="1">
@@ -27537,7 +28449,7 @@
       <c r="C15" s="1">
         <v>147196</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="22">
         <f t="shared" si="0"/>
         <v>-19106</v>
       </c>
@@ -27553,7 +28465,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -27562,7 +28474,7 @@
       <c r="C16" s="1">
         <v>130217</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="22">
         <f t="shared" si="0"/>
         <v>12955</v>
       </c>
@@ -27578,7 +28490,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="21" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -27587,7 +28499,7 @@
       <c r="C17" s="1">
         <v>137825</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="22">
         <f t="shared" si="0"/>
         <v>11539</v>
       </c>
@@ -27603,7 +28515,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="1">
@@ -27612,7 +28524,7 @@
       <c r="C18" s="1">
         <v>151520</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="22">
         <f t="shared" si="0"/>
         <v>-16575</v>
       </c>
@@ -27628,7 +28540,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46298</v>
       </c>
       <c r="B19" s="1">
@@ -27637,7 +28549,7 @@
       <c r="C19" s="1">
         <v>160798</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="22">
         <f t="shared" si="0"/>
         <v>-41387</v>
       </c>
@@ -27653,7 +28565,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -27662,7 +28574,7 @@
       <c r="C20" s="1">
         <v>174599</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="22">
         <f t="shared" si="0"/>
         <v>-67780</v>
       </c>
@@ -27678,7 +28590,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="3">
@@ -27687,8 +28599,8 @@
       <c r="C21" s="3">
         <v>161077</v>
       </c>
-      <c r="D21" s="40">
-        <f t="shared" ref="D21:D26" si="2">B21-C21</f>
+      <c r="D21" s="22">
+        <f t="shared" ref="D21:D27" si="2">B21-C21</f>
         <v>-62806</v>
       </c>
       <c r="E21" s="3">
@@ -27703,129 +28615,154 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="39">
         <v>95356</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="39">
         <v>168228</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="22">
         <f t="shared" si="2"/>
         <v>-72872</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="39">
         <v>-2915</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="39">
         <v>7151</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="39">
         <f t="shared" si="1"/>
         <v>-10066</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="40">
         <v>91560</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="40">
         <v>185302</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="22">
         <f t="shared" si="2"/>
         <v>-93742</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="40">
         <v>-3796</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="40">
         <v>17074</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="39">
         <f t="shared" si="1"/>
         <v>-20870</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>102114</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>185322</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="22">
         <f t="shared" si="2"/>
         <v>-83208</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>10554</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>20</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="39">
         <f t="shared" si="1"/>
         <v>10534</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46133</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>101386</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>195846</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="22">
         <f t="shared" si="2"/>
         <v>-94460</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="39">
         <v>-728</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="40">
         <v>10524</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="39">
         <f t="shared" si="1"/>
         <v>-11252</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>106530</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>208589</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="22">
         <f t="shared" si="2"/>
         <v>-102059</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>5144</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>12743</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="39">
         <f t="shared" si="1"/>
         <v>-7599</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>109035</v>
+      </c>
+      <c r="C27" s="3">
+        <v>170773</v>
+      </c>
+      <c r="D27" s="22">
+        <f t="shared" si="2"/>
+        <v>-61738</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2505</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-37816</v>
+      </c>
+      <c r="G27" s="39">
+        <f t="shared" si="1"/>
+        <v>40321</v>
       </c>
     </row>
   </sheetData>
@@ -27837,20 +28774,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDC40EE-8D54-47CC-9557-EC14C0D36988}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" style="15" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="5" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -27859,7 +28796,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -27868,12 +28805,12 @@
       <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="13">
         <v>45971</v>
       </c>
       <c r="B2" s="3">
@@ -27882,7 +28819,7 @@
       <c r="C2" s="3">
         <v>180786</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="24">
         <f>B2-C2</f>
         <v>-157635</v>
       </c>
@@ -27892,13 +28829,13 @@
       <c r="F2" s="3">
         <v>-5912</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="33">
         <f>E2-F2</f>
         <v>1877</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="13">
         <v>45979</v>
       </c>
       <c r="B3" s="3">
@@ -27907,8 +28844,8 @@
       <c r="C3" s="3">
         <v>173351</v>
       </c>
-      <c r="D3" s="42">
-        <f t="shared" ref="D3:D26" si="0">B3-C3</f>
+      <c r="D3" s="24">
+        <f t="shared" ref="D3:D27" si="0">B3-C3</f>
         <v>-149099</v>
       </c>
       <c r="E3" s="3">
@@ -27917,13 +28854,13 @@
       <c r="F3" s="3">
         <v>-7435</v>
       </c>
-      <c r="G3" s="3">
-        <f t="shared" ref="G3:G26" si="1">E3-F3</f>
+      <c r="G3" s="33">
+        <f t="shared" ref="G3:G27" si="1">E3-F3</f>
         <v>8536</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
+      <c r="A4" s="13">
         <v>45986</v>
       </c>
       <c r="B4" s="3">
@@ -27932,7 +28869,7 @@
       <c r="C4" s="3">
         <v>171852</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="24">
         <f t="shared" si="0"/>
         <v>-150414</v>
       </c>
@@ -27942,13 +28879,13 @@
       <c r="F4" s="3">
         <v>-1499</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="33">
         <f t="shared" si="1"/>
         <v>-1315</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="13">
         <v>45993</v>
       </c>
       <c r="B5" s="3">
@@ -27957,7 +28894,7 @@
       <c r="C5" s="3">
         <v>169094</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="24">
         <f t="shared" si="0"/>
         <v>-150047</v>
       </c>
@@ -27967,13 +28904,13 @@
       <c r="F5" s="3">
         <v>-2758</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="33">
         <f t="shared" si="1"/>
         <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6" s="13">
         <v>46000</v>
       </c>
       <c r="B6" s="3">
@@ -27982,7 +28919,7 @@
       <c r="C6" s="3">
         <v>146394</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="24">
         <f t="shared" si="0"/>
         <v>-130600</v>
       </c>
@@ -27992,13 +28929,13 @@
       <c r="F6" s="3">
         <v>-22700</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="33">
         <f t="shared" si="1"/>
         <v>19447</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="13">
         <v>46007</v>
       </c>
       <c r="B7" s="3">
@@ -28007,7 +28944,7 @@
       <c r="C7" s="3">
         <v>112293</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="24">
         <f t="shared" si="0"/>
         <v>-86640</v>
       </c>
@@ -28017,13 +28954,13 @@
       <c r="F7" s="3">
         <v>-34101</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="33">
         <f t="shared" si="1"/>
         <v>43960</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="13">
         <v>46014</v>
       </c>
       <c r="B8" s="3">
@@ -28032,7 +28969,7 @@
       <c r="C8" s="3">
         <v>97532</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="24">
         <f t="shared" si="0"/>
         <v>-55793</v>
       </c>
@@ -28042,13 +28979,13 @@
       <c r="F8" s="3">
         <v>-14761</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="33">
         <f t="shared" si="1"/>
         <v>30847</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="13">
         <v>46021</v>
       </c>
       <c r="B9" s="3">
@@ -28057,7 +28994,7 @@
       <c r="C9" s="3">
         <v>93298</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="24">
         <f t="shared" si="0"/>
         <v>-40511</v>
       </c>
@@ -28067,13 +29004,13 @@
       <c r="F9" s="3">
         <v>-4234</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="33">
         <f t="shared" si="1"/>
         <v>15282</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10" s="13">
         <v>46028</v>
       </c>
       <c r="B10" s="3">
@@ -28082,7 +29019,7 @@
       <c r="C10" s="3">
         <v>97516</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="24">
         <f t="shared" si="0"/>
         <v>-40585</v>
       </c>
@@ -28092,13 +29029,13 @@
       <c r="F10" s="3">
         <v>4218</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="33">
         <f t="shared" si="1"/>
         <v>-74</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="13">
         <v>46035</v>
       </c>
       <c r="B11" s="3">
@@ -28107,7 +29044,7 @@
       <c r="C11" s="3">
         <v>104955</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="24">
         <f t="shared" si="0"/>
         <v>-42250</v>
       </c>
@@ -28117,13 +29054,13 @@
       <c r="F11" s="3">
         <v>7439</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="33">
         <f t="shared" si="1"/>
         <v>-1665</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+      <c r="A12" s="13">
         <v>46042</v>
       </c>
       <c r="B12" s="3">
@@ -28132,7 +29069,7 @@
       <c r="C12" s="3">
         <v>101241</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="24">
         <f t="shared" si="0"/>
         <v>-41785</v>
       </c>
@@ -28142,13 +29079,13 @@
       <c r="F12" s="3">
         <v>-3714</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="33">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="13">
         <v>46049</v>
       </c>
       <c r="B13" s="3">
@@ -28157,7 +29094,7 @@
       <c r="C13" s="3">
         <v>93215</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="24">
         <f t="shared" si="0"/>
         <v>-16046</v>
       </c>
@@ -28167,13 +29104,13 @@
       <c r="F13" s="3">
         <v>-8026</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="33">
         <f t="shared" si="1"/>
         <v>25739</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="13">
         <v>46056</v>
       </c>
       <c r="B14" s="3">
@@ -28182,7 +29119,7 @@
       <c r="C14" s="3">
         <v>75267</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="24">
         <f t="shared" si="0"/>
         <v>2130</v>
       </c>
@@ -28192,13 +29129,13 @@
       <c r="F14" s="3">
         <v>-17948</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="33">
         <f t="shared" si="1"/>
         <v>18176</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="13">
         <v>46063</v>
       </c>
       <c r="B15" s="3">
@@ -28207,7 +29144,7 @@
       <c r="C15" s="3">
         <v>71278</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="24">
         <f t="shared" si="0"/>
         <v>13276</v>
       </c>
@@ -28217,13 +29154,13 @@
       <c r="F15" s="3">
         <v>-3989</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="33">
         <f t="shared" si="1"/>
         <v>11146</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
+      <c r="A16" s="13">
         <v>46070</v>
       </c>
       <c r="B16" s="3">
@@ -28232,7 +29169,7 @@
       <c r="C16" s="3">
         <v>63775</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="24">
         <f t="shared" si="0"/>
         <v>25826</v>
       </c>
@@ -28242,13 +29179,13 @@
       <c r="F16" s="3">
         <v>-7503</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="33">
         <f t="shared" si="1"/>
         <v>12550</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="13">
         <v>46077</v>
       </c>
       <c r="B17" s="3">
@@ -28257,7 +29194,7 @@
       <c r="C17" s="3">
         <v>65234</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="24">
         <f t="shared" si="0"/>
         <v>27578</v>
       </c>
@@ -28267,13 +29204,13 @@
       <c r="F17" s="3">
         <v>1459</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="33">
         <f t="shared" si="1"/>
         <v>1752</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="13">
         <v>46084</v>
       </c>
       <c r="B18" s="3">
@@ -28282,7 +29219,7 @@
       <c r="C18" s="3">
         <v>72958</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="24">
         <f t="shared" si="0"/>
         <v>21050</v>
       </c>
@@ -28292,13 +29229,13 @@
       <c r="F18" s="3">
         <v>7724</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="33">
         <f t="shared" si="1"/>
         <v>-6528</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="13">
         <v>46091</v>
       </c>
       <c r="B19" s="3">
@@ -28307,7 +29244,7 @@
       <c r="C19" s="3">
         <v>57740</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="24">
         <f t="shared" si="0"/>
         <v>36159</v>
       </c>
@@ -28317,13 +29254,13 @@
       <c r="F19" s="3">
         <v>-15218</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="33">
         <f t="shared" si="1"/>
         <v>15109</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="13">
         <v>46098</v>
       </c>
       <c r="B20" s="3">
@@ -28332,7 +29269,7 @@
       <c r="C20" s="3">
         <v>65621</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="24">
         <f t="shared" si="0"/>
         <v>886</v>
       </c>
@@ -28342,22 +29279,22 @@
       <c r="F20" s="3">
         <v>7881</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="33">
         <f t="shared" si="1"/>
         <v>-35273</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="13">
         <v>46105</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="3">
         <v>62382</v>
       </c>
       <c r="C21" s="3">
         <v>63984</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="24">
         <f t="shared" si="0"/>
         <v>-1602</v>
       </c>
@@ -28367,134 +29304,159 @@
       <c r="F21" s="3">
         <v>-1637</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="33">
         <f t="shared" si="1"/>
         <v>-2488</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
+      <c r="A22" s="13">
         <v>46112</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="3">
         <v>56421</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="3">
         <v>89105</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="30">
         <f t="shared" si="0"/>
         <v>-32684</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="3">
         <v>-5961</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="3">
         <v>25121</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="33">
         <f t="shared" si="1"/>
         <v>-31082</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>60714</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>116362</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="30">
         <f t="shared" si="0"/>
         <v>-55648</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>4293</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>27257</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="33">
         <f t="shared" si="1"/>
         <v>-22964</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="13">
         <v>46126</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>54249</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>132521</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="30">
         <f t="shared" si="0"/>
         <v>-78272</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>-6465</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>16159</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="33">
         <f t="shared" si="1"/>
         <v>-22624</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="13">
         <v>46133</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>60889</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>119723</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="30">
         <f t="shared" si="0"/>
         <v>-58834</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>6640</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>-12798</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="33">
         <f t="shared" si="1"/>
         <v>19438</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="13">
         <v>46140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>66517</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>104993</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="30">
         <f t="shared" si="0"/>
         <v>-38476</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>5628</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>-14730</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="33">
         <f t="shared" si="1"/>
         <v>20358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>73650</v>
+      </c>
+      <c r="C27" s="3">
+        <v>88309</v>
+      </c>
+      <c r="D27" s="30">
+        <f t="shared" si="0"/>
+        <v>-14659</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7133</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-16684</v>
+      </c>
+      <c r="G27" s="32">
+        <f t="shared" si="1"/>
+        <v>23817</v>
       </c>
     </row>
   </sheetData>
@@ -28505,664 +29467,689 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A07693-2708-497B-89D5-86A56CB2CAAA}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:7" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="42" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="45">
+      <c r="A2" s="43">
         <v>45971</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>28677</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>72746</v>
       </c>
-      <c r="D2" s="47">
-        <f>B2-C2</f>
+      <c r="D2" s="33">
+        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
         <v>-44069</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="3">
         <v>3363</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="3">
         <v>10020</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <f>E2-F2</f>
         <v>-6657</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="45">
+      <c r="A3" s="43">
         <v>45979</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>24211</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>73468</v>
       </c>
-      <c r="D3" s="47">
-        <f>B3-C3</f>
+      <c r="D3" s="33">
+        <f t="shared" si="0"/>
         <v>-49257</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="3">
         <v>-4466</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>722</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G26" si="0">E3-F3</f>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G27" si="1">E3-F3</f>
         <v>-5188</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="45">
+      <c r="A4" s="43">
         <v>45986</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="44">
         <v>23477</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>75548</v>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
+      <c r="D4" s="33">
+        <f t="shared" si="0"/>
         <v>-52071</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>-734</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>2080</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
+      <c r="G4" s="1">
+        <f t="shared" si="1"/>
         <v>-2814</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="45">
+      <c r="A5" s="43">
         <v>45993</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>18394</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>71510</v>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
+      <c r="D5" s="33">
+        <f t="shared" si="0"/>
         <v>-53116</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>-5083</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>-4038</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
+      <c r="G5" s="1">
+        <f t="shared" si="1"/>
         <v>-1045</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="45">
+      <c r="A6" s="43">
         <v>46000</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="3">
         <v>14333</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>71114</v>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
+      <c r="D6" s="33">
+        <f t="shared" si="0"/>
         <v>-56781</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="3">
         <v>-4061</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-396</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
+      <c r="G6" s="1">
+        <f t="shared" si="1"/>
         <v>-3665</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="45">
+      <c r="A7" s="43">
         <v>46007</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>8129</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="3">
         <v>56172</v>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
+      <c r="D7" s="33">
+        <f t="shared" si="0"/>
         <v>-48043</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>-6204</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>-14942</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
+      <c r="G7" s="1">
+        <f t="shared" si="1"/>
         <v>8738</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="45">
+      <c r="A8" s="43">
         <v>46014</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>9596</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="3">
         <v>53630</v>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
+      <c r="D8" s="33">
+        <f t="shared" si="0"/>
         <v>-44034</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="3">
         <v>1467</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>-2542</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
+      <c r="G8" s="1">
+        <f t="shared" si="1"/>
         <v>4009</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="45">
+      <c r="A9" s="43">
         <v>46021</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="3">
         <v>8706</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="3">
         <v>51960</v>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
+      <c r="D9" s="33">
+        <f t="shared" si="0"/>
         <v>-43254</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-890</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>-1670</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
+      <c r="G9" s="1">
+        <f t="shared" si="1"/>
         <v>780</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="45">
+      <c r="A10" s="43">
         <v>46028</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>12971</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>56334</v>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
+      <c r="D10" s="33">
+        <f t="shared" si="0"/>
         <v>-43363</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="3">
         <v>4265</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="3">
         <v>4374</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
+      <c r="G10" s="1">
+        <f t="shared" si="1"/>
         <v>-109</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="45">
+      <c r="A11" s="43">
         <v>46035</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>9613</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>58464</v>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
+      <c r="D11" s="33">
+        <f t="shared" si="0"/>
         <v>-48851</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="3">
         <v>-3358</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="3">
         <v>2130</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
+      <c r="G11" s="1">
+        <f t="shared" si="1"/>
         <v>-5488</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="45">
+      <c r="A12" s="43">
         <v>46042</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <v>13670</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>63280</v>
       </c>
-      <c r="D12" s="47">
-        <f>B12-C12</f>
+      <c r="D12" s="33">
+        <f t="shared" si="0"/>
         <v>-49610</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="3">
         <v>4057</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="3">
         <v>4816</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
+      <c r="G12" s="1">
+        <f t="shared" si="1"/>
         <v>-759</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="45">
+      <c r="A13" s="43">
         <v>46049</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="3">
         <v>12074</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="3">
         <v>59819</v>
       </c>
-      <c r="D13" s="47">
-        <f>B13-C13</f>
+      <c r="D13" s="33">
+        <f t="shared" si="0"/>
         <v>-47745</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="3">
         <v>-1596</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="3">
         <v>-3461</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
+      <c r="G13" s="1">
+        <f t="shared" si="1"/>
         <v>1865</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="45">
+      <c r="A14" s="43">
         <v>46056</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <v>11883</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>46177</v>
       </c>
-      <c r="D14" s="47">
-        <f>B14-C14</f>
+      <c r="D14" s="33">
+        <f t="shared" si="0"/>
         <v>-34294</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-191</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="3">
         <v>-13642</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
+      <c r="G14" s="1">
+        <f t="shared" si="1"/>
         <v>13451</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="45">
+      <c r="A15" s="43">
         <v>46063</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="3">
         <v>11801</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="3">
         <v>46720</v>
       </c>
-      <c r="D15" s="47">
-        <f>B15-C15</f>
+      <c r="D15" s="33">
+        <f t="shared" si="0"/>
         <v>-34919</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>-82</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>543</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
+      <c r="G15" s="1">
+        <f t="shared" si="1"/>
         <v>-625</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="45">
+      <c r="A16" s="43">
         <v>46070</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>11183</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>46196</v>
       </c>
-      <c r="D16" s="47">
-        <f>B16-C16</f>
+      <c r="D16" s="33">
+        <f t="shared" si="0"/>
         <v>-35013</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-618</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-524</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
+      <c r="G16" s="1">
+        <f t="shared" si="1"/>
         <v>-94</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="45">
+      <c r="A17" s="43">
         <v>46077</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="3">
         <v>13839</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>43406</v>
       </c>
-      <c r="D17" s="47">
-        <f>B17-C17</f>
+      <c r="D17" s="33">
+        <f t="shared" si="0"/>
         <v>-29567</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="3">
         <v>2656</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="3">
         <v>-2790</v>
       </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
+      <c r="G17" s="1">
+        <f t="shared" si="1"/>
         <v>5446</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="45">
+      <c r="A18" s="43">
         <v>46084</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="3">
         <v>13176</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="3">
         <v>47510</v>
       </c>
-      <c r="D18" s="47">
-        <f>B18-C18</f>
+      <c r="D18" s="33">
+        <f t="shared" si="0"/>
         <v>-34334</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>-663</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="3">
         <v>4104</v>
       </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
+      <c r="G18" s="1">
+        <f t="shared" si="1"/>
         <v>-4767</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="45">
+      <c r="A19" s="43">
         <v>46091</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="3">
         <v>10944</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>48055</v>
       </c>
-      <c r="D19" s="47">
-        <f>B19-C19</f>
+      <c r="D19" s="33">
+        <f t="shared" si="0"/>
         <v>-37111</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="3">
         <v>-2232</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>545</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="0"/>
+      <c r="G19" s="1">
+        <f t="shared" si="1"/>
         <v>-2777</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="45">
+      <c r="A20" s="43">
         <v>46098</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>10998</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>34055</v>
       </c>
-      <c r="D20" s="47">
-        <f>B20-C20</f>
+      <c r="D20" s="33">
+        <f t="shared" si="0"/>
         <v>-23057</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>54</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="3">
         <v>-14000</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
+      <c r="G20" s="1">
+        <f t="shared" si="1"/>
         <v>14054</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="45">
+      <c r="A21" s="43">
         <v>46105</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <v>10847</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>37853</v>
       </c>
-      <c r="D21" s="47">
-        <f>B21-C21</f>
+      <c r="D21" s="33">
+        <f t="shared" si="0"/>
         <v>-27006</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>-151</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="3">
         <v>3798</v>
       </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
+      <c r="G21" s="1">
+        <f t="shared" si="1"/>
         <v>-3949</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="45">
+      <c r="A22" s="43">
         <v>46112</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="3">
         <v>10663</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>39251</v>
       </c>
-      <c r="D22" s="47">
-        <f>B22-C22</f>
+      <c r="D22" s="33">
+        <f t="shared" si="0"/>
         <v>-28588</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="3">
         <v>-184</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="3">
         <v>1398</v>
       </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
+      <c r="G22" s="1">
+        <f t="shared" si="1"/>
         <v>-1582</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="45">
+      <c r="A23" s="43">
         <v>46119</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>12636</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>48711</v>
       </c>
-      <c r="D23" s="47">
-        <f>B23-C23</f>
+      <c r="D23" s="33">
+        <f t="shared" si="0"/>
         <v>-36075</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>1973</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>9460</v>
       </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
+      <c r="G23" s="1">
+        <f t="shared" si="1"/>
         <v>-7487</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="45">
+      <c r="A24" s="43">
         <v>46126</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>10112</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>52388</v>
       </c>
-      <c r="D24" s="47">
-        <f>B24-C24</f>
+      <c r="D24" s="33">
+        <f t="shared" si="0"/>
         <v>-42276</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>-2524</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>3677</v>
       </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
+      <c r="G24" s="1">
+        <f t="shared" si="1"/>
         <v>-6201</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="45">
+      <c r="A25" s="43">
         <v>46133</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>7917</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>56371</v>
       </c>
-      <c r="D25" s="47">
-        <f>B25-C25</f>
+      <c r="D25" s="33">
+        <f t="shared" si="0"/>
         <v>-48454</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>-2195</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>3983</v>
       </c>
-      <c r="G25">
-        <f t="shared" si="0"/>
+      <c r="G25" s="1">
+        <f t="shared" si="1"/>
         <v>-6178</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="45">
+      <c r="A26" s="43">
         <v>46140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>9044</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>55366</v>
       </c>
-      <c r="D26" s="47">
-        <f>B26-C26</f>
+      <c r="D26" s="33">
+        <f t="shared" si="0"/>
         <v>-46322</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="3">
         <v>1127</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>-1005</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
+        <f t="shared" si="1"/>
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="43">
+        <v>46147</v>
+      </c>
+      <c r="B27" s="3">
+        <v>9063</v>
+      </c>
+      <c r="C27" s="3">
+        <v>57314</v>
+      </c>
+      <c r="D27" s="32">
         <f t="shared" si="0"/>
-        <v>2132</v>
+        <v>-48251</v>
+      </c>
+      <c r="E27" s="3">
+        <v>19</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1948</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="1"/>
+        <v>-1929</v>
       </c>
     </row>
   </sheetData>
@@ -29173,7 +30160,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC5BCC2-0E7D-47AA-8D33-415F235882BE}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -29209,7 +30196,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="A2" s="11">
         <v>46140</v>
       </c>
       <c r="B2" s="7">
@@ -29231,6 +30218,43 @@
       <c r="G2" s="7">
         <f>E2-F2</f>
         <v>-4435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>46147</v>
+      </c>
+      <c r="B3">
+        <v>211814</v>
+      </c>
+      <c r="C3">
+        <v>48511</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" ref="D3:D5" si="0">B3-C3</f>
+        <v>163303</v>
+      </c>
+      <c r="E3">
+        <v>-4</v>
+      </c>
+      <c r="F3">
+        <v>3736</v>
+      </c>
+      <c r="G3" s="7">
+        <f>E3-F3</f>
+        <v>-3740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Max 3.xlsx
+++ b/Max 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EBFEE6-1A73-42A5-8608-FC56469CDF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82CF806-AE0C-403E-84E7-05783B902603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14685" windowHeight="16200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUR " sheetId="11" r:id="rId1"/>
@@ -234,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -306,9 +306,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -521,9 +518,9 @@
           </c:trendline>
           <c:cat>
             <c:strRef>
-              <c:f>'EUR '!$A$2:$A$28</c:f>
+              <c:f>'EUR '!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>10/11/2025</c:v>
                 </c:pt>
@@ -594,15 +591,12 @@
                   <c:v>4/14/2026</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4/14/2026</c:v>
+                  <c:v>4/21/2026</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4/21/2026</c:v>
+                  <c:v>4/28/2026</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4/28/2026</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>5/5/2026</c:v>
                 </c:pt>
               </c:strCache>
@@ -610,10 +604,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'EUR '!$D$2:$D$28</c:f>
+              <c:f>'EUR '!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>73589</c:v>
                 </c:pt>
@@ -681,18 +675,15 @@
                   <c:v>-7541</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>65075</c:v>
+                  <c:v>26018</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>26018</c:v>
+                  <c:v>41324</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>41324</c:v>
+                  <c:v>35712</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>35712</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>32202</c:v>
                 </c:pt>
               </c:numCache>
@@ -24495,7 +24486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0DCE6A-E542-4A83-ACFA-B4956F29450C}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="15" customWidth="1"/>
@@ -24541,7 +24532,7 @@
         <v>162331</v>
       </c>
       <c r="D2" s="28">
-        <f t="shared" ref="D2:D28" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D27" si="0">B2-C2</f>
         <v>73589</v>
       </c>
       <c r="E2" s="1">
@@ -24551,7 +24542,7 @@
         <v>1584</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G28" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G27" si="1">E2-F2</f>
         <v>-18206</v>
       </c>
     </row>
@@ -25081,132 +25072,107 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="37">
+      <c r="A24" s="13">
         <v>46126</v>
       </c>
       <c r="B24" s="3">
-        <v>129517</v>
+        <v>214639</v>
       </c>
       <c r="C24" s="3">
-        <v>64442</v>
+        <v>188621</v>
       </c>
       <c r="D24" s="28">
         <f t="shared" si="0"/>
-        <v>65075</v>
+        <v>26018</v>
       </c>
       <c r="E24" s="3">
-        <v>-8442</v>
+        <v>13693</v>
       </c>
       <c r="F24" s="3">
-        <v>-2704</v>
+        <v>-19866</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="1"/>
-        <v>-5738</v>
+        <v>33559</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="B25" s="3">
-        <v>214639</v>
+        <v>217407</v>
       </c>
       <c r="C25" s="3">
-        <v>188621</v>
+        <v>176083</v>
       </c>
       <c r="D25" s="28">
         <f t="shared" si="0"/>
-        <v>26018</v>
+        <v>41324</v>
       </c>
       <c r="E25" s="3">
-        <v>13693</v>
+        <v>2768</v>
       </c>
       <c r="F25" s="3">
-        <v>-19866</v>
+        <v>-12538</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="1"/>
-        <v>33559</v>
+        <v>15306</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="B26" s="3">
-        <v>217407</v>
+        <v>217091</v>
       </c>
       <c r="C26" s="3">
-        <v>176083</v>
+        <v>181379</v>
       </c>
       <c r="D26" s="28">
         <f t="shared" si="0"/>
-        <v>41324</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2768</v>
+        <v>35712</v>
+      </c>
+      <c r="E26" s="1">
+        <v>-316</v>
       </c>
       <c r="F26" s="3">
-        <v>-12538</v>
+        <v>5296</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="1"/>
-        <v>15306</v>
+        <v>-5612</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
-        <v>46140</v>
+        <v>46147</v>
       </c>
       <c r="B27" s="3">
-        <v>217091</v>
+        <v>217474</v>
       </c>
       <c r="C27" s="3">
-        <v>181379</v>
+        <v>185272</v>
       </c>
       <c r="D27" s="28">
         <f t="shared" si="0"/>
-        <v>35712</v>
-      </c>
-      <c r="E27" s="1">
-        <v>-316</v>
+        <v>32202</v>
+      </c>
+      <c r="E27" s="3">
+        <v>383</v>
       </c>
       <c r="F27" s="3">
-        <v>5296</v>
+        <v>3893</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="1"/>
-        <v>-5612</v>
+        <v>-3510</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
-        <v>46147</v>
-      </c>
-      <c r="B28" s="3">
-        <v>217474</v>
-      </c>
-      <c r="C28" s="3">
-        <v>185272</v>
-      </c>
-      <c r="D28" s="28">
-        <f t="shared" si="0"/>
-        <v>32202</v>
-      </c>
-      <c r="E28" s="3">
-        <v>383</v>
-      </c>
-      <c r="F28" s="3">
-        <v>3893</v>
-      </c>
-      <c r="G28" s="1">
-        <f t="shared" si="1"/>
-        <v>-3510</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F29" s="17"/>
+      <c r="F28" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -26664,20 +26630,20 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="45">
+      <c r="A27" s="44">
         <v>46154</v>
       </c>
-      <c r="B27" s="46">
+      <c r="B27" s="45">
         <v>150800</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="45">
         <v>65810</v>
       </c>
       <c r="D27" s="30">
         <f t="shared" si="0"/>
         <v>84990</v>
       </c>
-      <c r="E27" s="47"/>
+      <c r="E27" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27357,7 +27323,7 @@
       <c r="C27" s="3">
         <v>41666</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <f t="shared" si="0"/>
         <v>-34521</v>
       </c>
@@ -28618,23 +28584,23 @@
       <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="38">
         <v>95356</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="38">
         <v>168228</v>
       </c>
       <c r="D22" s="22">
         <f t="shared" si="2"/>
         <v>-72872</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="38">
         <v>-2915</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="38">
         <v>7151</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="38">
         <f t="shared" si="1"/>
         <v>-10066</v>
       </c>
@@ -28643,23 +28609,23 @@
       <c r="A23" s="13">
         <v>46119</v>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="39">
         <v>91560</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="39">
         <v>185302</v>
       </c>
       <c r="D23" s="22">
         <f t="shared" si="2"/>
         <v>-93742</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="39">
         <v>-3796</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="39">
         <v>17074</v>
       </c>
-      <c r="G23" s="39">
+      <c r="G23" s="38">
         <f t="shared" si="1"/>
         <v>-20870</v>
       </c>
@@ -28685,7 +28651,7 @@
       <c r="F24" s="1">
         <v>20</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="38">
         <f t="shared" si="1"/>
         <v>10534</v>
       </c>
@@ -28704,13 +28670,13 @@
         <f t="shared" si="2"/>
         <v>-94460</v>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="38">
         <v>-728</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="39">
         <v>10524</v>
       </c>
-      <c r="G25" s="39">
+      <c r="G25" s="38">
         <f t="shared" si="1"/>
         <v>-11252</v>
       </c>
@@ -28735,7 +28701,7 @@
       <c r="F26" s="3">
         <v>12743</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="38">
         <f t="shared" si="1"/>
         <v>-7599</v>
       </c>
@@ -28760,7 +28726,7 @@
       <c r="F27" s="1">
         <v>-37816</v>
       </c>
-      <c r="G27" s="39">
+      <c r="G27" s="38">
         <f t="shared" si="1"/>
         <v>40321</v>
       </c>
@@ -29480,30 +29446,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="41" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="42">
         <v>45971</v>
       </c>
       <c r="B2" s="3">
@@ -29528,7 +29494,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="43">
+      <c r="A3" s="42">
         <v>45979</v>
       </c>
       <c r="B3" s="3">
@@ -29553,10 +29519,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="43">
+      <c r="A4" s="42">
         <v>45986</v>
       </c>
-      <c r="B4" s="44">
+      <c r="B4" s="43">
         <v>23477</v>
       </c>
       <c r="C4" s="3">
@@ -29578,7 +29544,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="43">
+      <c r="A5" s="42">
         <v>45993</v>
       </c>
       <c r="B5" s="3">
@@ -29603,7 +29569,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
+      <c r="A6" s="42">
         <v>46000</v>
       </c>
       <c r="B6" s="3">
@@ -29628,7 +29594,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
+      <c r="A7" s="42">
         <v>46007</v>
       </c>
       <c r="B7" s="3">
@@ -29653,7 +29619,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
+      <c r="A8" s="42">
         <v>46014</v>
       </c>
       <c r="B8" s="3">
@@ -29678,7 +29644,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
+      <c r="A9" s="42">
         <v>46021</v>
       </c>
       <c r="B9" s="3">
@@ -29703,7 +29669,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="42">
         <v>46028</v>
       </c>
       <c r="B10" s="3">
@@ -29728,7 +29694,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="42">
         <v>46035</v>
       </c>
       <c r="B11" s="3">
@@ -29753,7 +29719,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="42">
         <v>46042</v>
       </c>
       <c r="B12" s="3">
@@ -29778,7 +29744,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
+      <c r="A13" s="42">
         <v>46049</v>
       </c>
       <c r="B13" s="3">
@@ -29803,7 +29769,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
+      <c r="A14" s="42">
         <v>46056</v>
       </c>
       <c r="B14" s="3">
@@ -29828,7 +29794,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
+      <c r="A15" s="42">
         <v>46063</v>
       </c>
       <c r="B15" s="3">
@@ -29853,7 +29819,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="42">
         <v>46070</v>
       </c>
       <c r="B16" s="3">
@@ -29878,7 +29844,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
+      <c r="A17" s="42">
         <v>46077</v>
       </c>
       <c r="B17" s="3">
@@ -29903,7 +29869,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="A18" s="42">
         <v>46084</v>
       </c>
       <c r="B18" s="3">
@@ -29928,7 +29894,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
+      <c r="A19" s="42">
         <v>46091</v>
       </c>
       <c r="B19" s="3">
@@ -29953,7 +29919,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
+      <c r="A20" s="42">
         <v>46098</v>
       </c>
       <c r="B20" s="3">
@@ -29978,7 +29944,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="43">
+      <c r="A21" s="42">
         <v>46105</v>
       </c>
       <c r="B21" s="3">
@@ -30003,7 +29969,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+      <c r="A22" s="42">
         <v>46112</v>
       </c>
       <c r="B22" s="3">
@@ -30028,7 +29994,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="43">
+      <c r="A23" s="42">
         <v>46119</v>
       </c>
       <c r="B23" s="3">
@@ -30053,7 +30019,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="43">
+      <c r="A24" s="42">
         <v>46126</v>
       </c>
       <c r="B24" s="3">
@@ -30078,7 +30044,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="43">
+      <c r="A25" s="42">
         <v>46133</v>
       </c>
       <c r="B25" s="3">
@@ -30103,7 +30069,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
+      <c r="A26" s="42">
         <v>46140</v>
       </c>
       <c r="B26" s="3">
@@ -30128,7 +30094,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="43">
+      <c r="A27" s="42">
         <v>46147</v>
       </c>
       <c r="B27" s="3">
